--- a/languages/es/output/import/西班牙语专四进阶.xlsx
+++ b/languages/es/output/import/西班牙语专四进阶.xlsx
@@ -69119,7 +69119,7 @@
       </c>
       <c r="B2153" s="1" t="inlineStr">
         <is>
-          <t>[hoˈɾmi.ɡa/ [hoɾˈmi.ɣ̞a]] 蚂蚁&lt;名&gt;</t>
+          <t>[hoˈɾmi.ɡa] 蚂蚁&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2153" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专四进阶.xlsx
+++ b/languages/es/output/import/西班牙语专四进阶.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,7 +691,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>[ˈpunta] 小费&lt;名&gt;</t>
+          <t>[/ˈpunta/] 尖端；顶端；尖头&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>小费</t>
+          <t>尖端；顶端；尖头</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>[senˈtada] 坐着&lt;名&gt;</t>
+          <t>[/senˈtada/] 坐着的；一次坐（sentar的过去分词阴性）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>坐着</t>
+          <t>坐着的；一次坐（sentar的过去分词阴性）</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -1619,13 +1619,17 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>吉恩&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr"/>
+          <t>[[ˈʝin] 牛仔裤&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>/xˈean/</t>
+        </is>
+      </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>吉恩</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1650,7 +1654,11 @@
           <t>古代的&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr"/>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>/anˈtiɡwos/</t>
+        </is>
+      </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
           <t>古代的</t>
@@ -1867,7 +1875,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>[koˈxones] 球&lt;名&gt;</t>
+          <t>[/koˈxones/] 睾丸；胆量（粗俗）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1877,7 +1885,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>球</t>
+          <t>睾丸；胆量（粗俗）</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2251,7 +2259,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>[ˈplaθa] 正方形&lt;名&gt;</t>
+          <t>[/ˈplaθa/] 广场&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2261,7 +2269,7 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>正方形</t>
+          <t>广场</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2699,7 +2707,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>[ˈkole] 科尔&lt;名&gt;</t>
+          <t>[/ˈkole/] 学校（口语）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2709,7 +2717,7 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>科尔</t>
+          <t>学校（口语）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2763,7 +2771,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>[ˈpinta] 品脱&lt;名&gt;</t>
+          <t>[/ˈpinta/] 外观；油漆&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2773,7 +2781,7 @@
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>品脱</t>
+          <t>外观；油漆&lt;名&gt;</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -2923,7 +2931,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>[esˈkape] 排气&lt;名&gt;</t>
+          <t>[/esˈkape/] 逃跑；逃脱；排气管&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2933,7 +2941,7 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>排气</t>
+          <t>逃跑；逃脱；排气管</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -3051,7 +3059,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>[kaˈida] 秋天&lt;名&gt;</t>
+          <t>[kaˈida] 落下；跌倒；下降；垮台&lt;名&gt;</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -3061,7 +3069,7 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>秋天</t>
+          <t>落下；跌倒；下降；垮台</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -3118,7 +3126,11 @@
           <t>有&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr"/>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>/abˈia/</t>
+        </is>
+      </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
           <t>有</t>
@@ -3399,7 +3411,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>[kosˈtumbɾe] 定制&lt;名&gt;</t>
+          <t>[kosˈtumbɾe] 习惯；风俗&lt;名&gt;</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3409,7 +3421,7 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>定制</t>
+          <t>习惯；风俗</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -3943,7 +3955,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>[apeteˈθeɾ] 花哨的&lt;动&gt;</t>
+          <t>[apeteˈθeɾ] 渴望；想要；引起食欲&lt;动&gt;</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3953,7 +3965,7 @@
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>花哨的</t>
+          <t>渴望；想要；引起食欲</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -4458,7 +4470,11 @@
           <t>兴趣&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr"/>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>/intˈeɾes/</t>
+        </is>
+      </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
           <t>兴趣</t>
@@ -4611,7 +4627,7 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾima] 表弟&lt;名&gt;</t>
+          <t>[ˈpɾima] 表姐妹；堂姐妹&lt;名&gt;</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -4621,7 +4637,7 @@
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>表弟</t>
+          <t>表姐妹；堂姐妹</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
@@ -4835,7 +4851,7 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>[ˈman] 男人&lt;名&gt;</t>
+          <t>[ˈman] 老兄；哥们&lt;名&gt;</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4845,7 +4861,7 @@
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>男人</t>
+          <t>老兄；哥们</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
@@ -5187,7 +5203,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>[benˈdaɾ] 绷带&lt;动&gt;</t>
+          <t>[benˈdaɾ] 包扎；用绷带包扎&lt;动&gt;</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -5197,7 +5213,7 @@
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>绷带</t>
+          <t>包扎；用绷带包扎</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -5510,7 +5526,11 @@
           <t>超级&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr"/>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>/supˈeɾ/</t>
+        </is>
+      </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
           <t>超级</t>
@@ -5727,7 +5747,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>[emˈpjeθo] 我开始&lt;名&gt;</t>
+          <t>[/emˈpjeθo/] 开始&lt;动&gt;（empezar的第一人称单数）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5737,7 +5757,7 @@
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>我开始</t>
+          <t>开始&lt;动&gt;（empezar的第一人称单数）</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -5890,7 +5910,11 @@
           <t>正式&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr"/>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>/ofiθjalˈmente/</t>
+        </is>
+      </c>
       <c r="D172" s="1" t="inlineStr">
         <is>
           <t>正式</t>
@@ -5947,7 +5971,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>[ˈrumbo] 课程&lt;名&gt;</t>
+          <t>[ˈrumbo] 方向；航向&lt;名&gt;</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5957,7 +5981,7 @@
       </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>课程</t>
+          <t>方向；航向</t>
         </is>
       </c>
       <c r="E174" s="1" t="inlineStr">
@@ -6459,7 +6483,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>[enoɾaˈbwena] 恭喜&lt;名&gt;</t>
+          <t>[/enoɾaˈbwena/] 恭喜&lt;叹&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -6469,7 +6493,7 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>恭喜</t>
+          <t>恭喜&lt;叹&gt;</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -6491,7 +6515,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>[ˈanimo] 鼓励&lt;名&gt;</t>
+          <t>[/ˈanimo/] 精神；勇气&lt;名&gt;；加油&lt;叹&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -6501,7 +6525,7 @@
       </c>
       <c r="D191" s="1" t="inlineStr">
         <is>
-          <t>鼓励</t>
+          <t>精神；勇气&lt;名&gt;；加油&lt;叹&gt;</t>
         </is>
       </c>
       <c r="E191" s="1" t="inlineStr">
@@ -6619,7 +6643,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>[despeˈxado] 清晰&lt;形&gt;</t>
+          <t>[/despeˈxado/] 晴朗的；清澈的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -6629,7 +6653,7 @@
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>清晰</t>
+          <t>晴朗的；清澈的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
@@ -6971,7 +6995,7 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>[ˈpwesta] 把&lt;名&gt;</t>
+          <t>[ˈpwesta] 放置；落山；日落&lt;名&gt;</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
@@ -6981,7 +7005,7 @@
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t>把</t>
+          <t>放置；落山；日落</t>
         </is>
       </c>
       <c r="E206" s="1" t="inlineStr">
@@ -7035,7 +7059,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>[pɾostiˈtuto] 妓女&lt;名&gt;</t>
+          <t>[pɾostiˈtuto] 男妓&lt;名&gt;</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -7045,7 +7069,7 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>妓女</t>
+          <t>男妓</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -7355,7 +7379,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[eˈleno] 埃莱诺&lt;名&gt;</t>
+          <t>[/eˈleno/] 希腊的&lt;形&gt;；希腊人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -7365,7 +7389,7 @@
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>埃莱诺</t>
+          <t>希腊的&lt;形&gt;；希腊人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -7451,7 +7475,7 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>[arwiˈnaɾ] 废墟&lt;动&gt;</t>
+          <t>[arwiˈnaɾ] 毁坏；破坏；使破产&lt;动&gt;</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -7461,7 +7485,7 @@
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>废墟</t>
+          <t>毁坏；破坏；使破产</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
@@ -8606,7 +8630,11 @@
           <t>毫米&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C257" s="1" t="inlineStr"/>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>/ˈeme ˈeme/</t>
+        </is>
+      </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
           <t>毫米</t>
@@ -8983,7 +9011,7 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>[poˈneɾle] 把&lt;动&gt;</t>
+          <t>[poˈneɾle] 给…加上；给…放上&lt;动&gt;</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
@@ -8993,7 +9021,7 @@
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>把</t>
+          <t>给…加上；给…放上</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
@@ -9015,7 +9043,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>[emˈpjeθe] 开始&lt;名&gt;</t>
+          <t>[/emˈpjeθe/] 开始（empezar 的虚拟式现在时）&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
@@ -9025,7 +9053,7 @@
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>开始</t>
+          <t>开始（empezar 的虚拟式现在时）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
@@ -9239,7 +9267,7 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>[ˈpoθo] 嗯&lt;名&gt;</t>
+          <t>[ˈpoθo] 井；水井；矿井；坑&lt;名&gt;</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
@@ -9249,7 +9277,7 @@
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>嗯</t>
+          <t>井；水井；矿井；坑</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
@@ -10106,7 +10134,11 @@
           <t>那里&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C304" s="1" t="inlineStr"/>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>/ˈaʝi/</t>
+        </is>
+      </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
           <t>那里</t>
@@ -10451,7 +10483,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>[ˈuɲa] 钉子&lt;名&gt;</t>
+          <t>[ˈuɲa] 指甲；趾甲&lt;名&gt;</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -10461,7 +10493,7 @@
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t>钉子</t>
+          <t>指甲；趾甲</t>
         </is>
       </c>
       <c r="E315" s="1" t="inlineStr">
@@ -10483,7 +10515,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>[enkaɾˈɡaɾ] 订单&lt;动&gt;</t>
+          <t>[enkaɾˈɡaɾ] 委托；订购；负责&lt;动&gt;</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -10493,7 +10525,7 @@
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t>订单</t>
+          <t>委托；订购；负责</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
@@ -10643,7 +10675,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>[ˈteɡsto] 文字&lt;名&gt;</t>
+          <t>[/ˈteɡsto/] 文本&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -10653,7 +10685,7 @@
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E321" s="1" t="inlineStr">
@@ -11091,7 +11123,7 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>[noˈtaɾ] 通知&lt;动&gt;</t>
+          <t>[noˈtaɾ] 注意到；察觉&lt;动&gt;</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
@@ -11101,7 +11133,7 @@
       </c>
       <c r="D335" s="1" t="inlineStr">
         <is>
-          <t>通知</t>
+          <t>注意到；察觉</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
@@ -11187,7 +11219,7 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t>[kuˈbɾiɾ] 封面&lt;动&gt;</t>
+          <t>[/kuˈbɾiɾ/] 覆盖；遮盖；掩盖&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
@@ -11197,7 +11229,7 @@
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t>封面</t>
+          <t>覆盖；遮盖；掩盖</t>
         </is>
       </c>
       <c r="E338" s="1" t="inlineStr">
@@ -11539,7 +11571,7 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>[konsideˈɾando] 考虑到&lt;名&gt;</t>
+          <t>[/konsideˈɾando/] 考虑到，鉴于&lt;名&gt;（公文中的引言部分）；considerar 的副动词形式&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
@@ -11549,7 +11581,7 @@
       </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t>考虑到</t>
+          <t>考虑到，鉴于&lt;名&gt;（公文中的引言部分）；considerar 的副动词形式</t>
         </is>
       </c>
       <c r="E349" s="1" t="inlineStr">
@@ -12115,7 +12147,7 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>[liˈdjaɾ] 交易&lt;动&gt;</t>
+          <t>[/liˈdjaɾ/] 处理；应对；斗牛&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
@@ -12125,7 +12157,7 @@
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t>交易</t>
+          <t>处理；应对；斗牛</t>
         </is>
       </c>
       <c r="E367" s="1" t="inlineStr">
@@ -12147,7 +12179,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>[senˈtenθja] 句子&lt;名&gt;</t>
+          <t>[/senˈtenθja/] 判决；裁决；格言&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
@@ -12157,7 +12189,7 @@
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t>句子</t>
+          <t>判决；裁决；格言</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
@@ -12531,7 +12563,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>[komeˈteɾ] 提交&lt;动&gt;</t>
+          <t>[/komeˈteɾ/] 犯（错误、罪行）；做（错事）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
@@ -12541,7 +12573,7 @@
       </c>
       <c r="D380" s="1" t="inlineStr">
         <is>
-          <t>提交</t>
+          <t>犯（错误、罪行）；做（错事）</t>
         </is>
       </c>
       <c r="E380" s="1" t="inlineStr">
@@ -12726,7 +12758,11 @@
           <t>丝袜&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C386" s="1" t="inlineStr"/>
+      <c r="C386" s="1" t="inlineStr">
+        <is>
+          <t>/ˈmejas/</t>
+        </is>
+      </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
           <t>丝袜</t>
@@ -13362,7 +13398,11 @@
           <t>柏林&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C406" s="1" t="inlineStr"/>
+      <c r="C406" s="1" t="inlineStr">
+        <is>
+          <t>/beɾlˈin/</t>
+        </is>
+      </c>
       <c r="D406" s="1" t="inlineStr">
         <is>
           <t>柏林</t>
@@ -13387,7 +13427,7 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>[kaˈɲon] 大炮&lt;形&gt;</t>
+          <t>[/kaˈɲon/] 大炮；峡谷&lt;名&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C407" s="1" t="inlineStr">
@@ -13397,7 +13437,7 @@
       </c>
       <c r="D407" s="1" t="inlineStr">
         <is>
-          <t>大炮</t>
+          <t>大炮；峡谷&lt;名&gt;</t>
         </is>
       </c>
       <c r="E407" s="1" t="inlineStr">
@@ -13547,7 +13587,7 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡɾita] 尖叫&lt;名&gt;</t>
+          <t>[/ˈɡɾita/] 喊叫&lt;动&gt;（gritar 的第三人称单数变位）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
@@ -13557,7 +13597,7 @@
       </c>
       <c r="D412" s="1" t="inlineStr">
         <is>
-          <t>尖叫</t>
+          <t>喊叫&lt;动&gt;（gritar 的第三人称单数变位）</t>
         </is>
       </c>
       <c r="E412" s="1" t="inlineStr">
@@ -13739,7 +13779,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>[ˈrob] 罗布&lt;名&gt;</t>
+          <t>[/ˈrob/] 抢劫；偷窃&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
@@ -13749,7 +13789,7 @@
       </c>
       <c r="D418" s="1" t="inlineStr">
         <is>
-          <t>罗布</t>
+          <t>抢劫；偷窃</t>
         </is>
       </c>
       <c r="E418" s="1" t="inlineStr">
@@ -13931,13 +13971,17 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>所以&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C424" s="1" t="inlineStr"/>
+          <t>[[so] （口语贬义前缀）这个；所谓的&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C424" s="1" t="inlineStr">
+        <is>
+          <t>/so/</t>
+        </is>
+      </c>
       <c r="D424" s="1" t="inlineStr">
         <is>
-          <t>所以</t>
+          <t>（口语贬义前缀）这个；所谓的</t>
         </is>
       </c>
       <c r="E424" s="1" t="inlineStr">
@@ -14343,7 +14387,7 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t>[kauˈsaɾ] 原因&lt;动&gt;</t>
+          <t>[/kauˈsaɾ/] 引起；导致；造成&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C437" s="1" t="inlineStr">
@@ -14353,7 +14397,7 @@
       </c>
       <c r="D437" s="1" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>引起；导致；造成</t>
         </is>
       </c>
       <c r="E437" s="1" t="inlineStr">
@@ -14375,7 +14419,7 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>[bixiˈlaɾ] 手表&lt;动&gt;</t>
+          <t>[/bixiˈlaɾ/] 监视；看守；警戒&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
@@ -14385,7 +14429,7 @@
       </c>
       <c r="D438" s="1" t="inlineStr">
         <is>
-          <t>手表</t>
+          <t>监视；看守；警戒</t>
         </is>
       </c>
       <c r="E438" s="1" t="inlineStr">
@@ -14631,7 +14675,7 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>[foɾˈmaɾ] 形式&lt;动&gt;</t>
+          <t>[/foɾˈmaɾ/] 形成；组成；培养&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
@@ -14641,7 +14685,7 @@
       </c>
       <c r="D446" s="1" t="inlineStr">
         <is>
-          <t>形式</t>
+          <t>形成；组成；培养</t>
         </is>
       </c>
       <c r="E446" s="1" t="inlineStr">
@@ -14727,7 +14771,7 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>[testaˈmento] 会&lt;名&gt;</t>
+          <t>[/testaˈmento/] 遗嘱；圣约&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
@@ -14737,7 +14781,7 @@
       </c>
       <c r="D449" s="1" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>遗嘱；圣约</t>
         </is>
       </c>
       <c r="E449" s="1" t="inlineStr">
@@ -14887,7 +14931,7 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t>[ˈroso] 粉红色&lt;形&gt;</t>
+          <t>[/ˈroso/] rosa 粉红色的&lt;形&gt;（roso 非标准词）&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C454" s="1" t="inlineStr">
@@ -14897,7 +14941,7 @@
       </c>
       <c r="D454" s="1" t="inlineStr">
         <is>
-          <t>粉红色</t>
+          <t>rosa 粉红色的&lt;形&gt;（roso 非标准词）</t>
         </is>
       </c>
       <c r="E454" s="1" t="inlineStr">
@@ -15335,7 +15379,7 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>[roˈmanθe] 浪漫&lt;名&gt;</t>
+          <t>[/roˈmanθe/] 罗曼语族的语言；西班牙民谣&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
@@ -15345,7 +15389,7 @@
       </c>
       <c r="D468" s="1" t="inlineStr">
         <is>
-          <t>浪漫</t>
+          <t>罗曼语族的语言；西班牙民谣&lt;名&gt;</t>
         </is>
       </c>
       <c r="E468" s="1" t="inlineStr">
@@ -15367,7 +15411,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>[ˈmjente] 谎言&lt;名&gt;</t>
+          <t>[/ˈmjente/] 说谎；撒谎&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C469" s="1" t="inlineStr">
@@ -15377,7 +15421,7 @@
       </c>
       <c r="D469" s="1" t="inlineStr">
         <is>
-          <t>谎言</t>
+          <t>说谎；撒谎</t>
         </is>
       </c>
       <c r="E469" s="1" t="inlineStr">
@@ -15495,7 +15539,7 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t>[ˈmonte] 安装&lt;名&gt;</t>
+          <t>[/ˈmonte/] 山；山林；山地&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C473" s="1" t="inlineStr">
@@ -15505,7 +15549,7 @@
       </c>
       <c r="D473" s="1" t="inlineStr">
         <is>
-          <t>安装</t>
+          <t>山；山林；山地</t>
         </is>
       </c>
       <c r="E473" s="1" t="inlineStr">
@@ -15559,7 +15603,7 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t>[enteˈɾaɾ] 找出来&lt;动&gt;</t>
+          <t>[/enteˈɾaɾ/] 告知；通知；使得知&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C475" s="1" t="inlineStr">
@@ -15569,7 +15613,7 @@
       </c>
       <c r="D475" s="1" t="inlineStr">
         <is>
-          <t>找出来</t>
+          <t>告知；通知；使得知</t>
         </is>
       </c>
       <c r="E475" s="1" t="inlineStr">
@@ -15847,7 +15891,7 @@
       </c>
       <c r="B484" s="1" t="inlineStr">
         <is>
-          <t>[pesˈkaɾ] 鱼&lt;动&gt;</t>
+          <t>[/pesˈkaɾ/] 捕鱼；钓鱼&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C484" s="1" t="inlineStr">
@@ -15857,7 +15901,7 @@
       </c>
       <c r="D484" s="1" t="inlineStr">
         <is>
-          <t>鱼</t>
+          <t>捕鱼；钓鱼</t>
         </is>
       </c>
       <c r="E484" s="1" t="inlineStr">
@@ -15911,7 +15955,7 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>[paˈɾexo] 甚至&lt;形&gt;</t>
+          <t>[/paˈɾexo/] 均匀的；平坦的；相等的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C486" s="1" t="inlineStr">
@@ -15921,7 +15965,7 @@
       </c>
       <c r="D486" s="1" t="inlineStr">
         <is>
-          <t>甚至</t>
+          <t>均匀的；平坦的；相等的</t>
         </is>
       </c>
       <c r="E486" s="1" t="inlineStr">
@@ -16167,7 +16211,7 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t>[ˈplaθo] 术语&lt;名&gt;</t>
+          <t>[ˈplaθo] 期限；期间&lt;名&gt;</t>
         </is>
       </c>
       <c r="C494" s="1" t="inlineStr">
@@ -16177,7 +16221,7 @@
       </c>
       <c r="D494" s="1" t="inlineStr">
         <is>
-          <t>术语</t>
+          <t>期限；期间</t>
         </is>
       </c>
       <c r="E494" s="1" t="inlineStr">
@@ -16487,13 +16531,17 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>上午&lt;副&gt;</t>
-        </is>
-      </c>
-      <c r="C504" s="1" t="inlineStr"/>
+          <t>是&lt;副&gt;</t>
+        </is>
+      </c>
+      <c r="C504" s="1" t="inlineStr">
+        <is>
+          <t>/ˈam/</t>
+        </is>
+      </c>
       <c r="D504" s="1" t="inlineStr">
         <is>
-          <t>上午</t>
+          <t>是</t>
         </is>
       </c>
       <c r="E504" s="1" t="inlineStr">
@@ -16899,7 +16947,7 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t>[ˈranɡo] 范围&lt;名&gt;</t>
+          <t>[/ˈranɡo/] 等级、级别&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C517" s="1" t="inlineStr">
@@ -16909,7 +16957,7 @@
       </c>
       <c r="D517" s="1" t="inlineStr">
         <is>
-          <t>范围</t>
+          <t>等级、级别&lt;名&gt;</t>
         </is>
       </c>
       <c r="E517" s="1" t="inlineStr">
@@ -17539,7 +17587,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>[aɡɾaˈdaɾ] 请&lt;动&gt;</t>
+          <t>[aɡɾaˈdaɾ] 使喜爱；取悦；使满意&lt;动&gt;</t>
         </is>
       </c>
       <c r="C537" s="1" t="inlineStr">
@@ -17549,7 +17597,7 @@
       </c>
       <c r="D537" s="1" t="inlineStr">
         <is>
-          <t>请</t>
+          <t>使喜爱；取悦；使满意</t>
         </is>
       </c>
       <c r="E537" s="1" t="inlineStr">
@@ -18118,7 +18166,11 @@
           <t>困难&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C555" s="1" t="inlineStr"/>
+      <c r="C555" s="1" t="inlineStr">
+        <is>
+          <t>/difiθˈil/</t>
+        </is>
+      </c>
       <c r="D555" s="1" t="inlineStr">
         <is>
           <t>困难</t>
@@ -18434,7 +18486,11 @@
           <t>给了&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C565" s="1" t="inlineStr"/>
+      <c r="C565" s="1" t="inlineStr">
+        <is>
+          <t>/diˈo/</t>
+        </is>
+      </c>
       <c r="D565" s="1" t="inlineStr">
         <is>
           <t>给了</t>
@@ -18811,7 +18867,7 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>[ˈkapa] 海角&lt;名&gt;</t>
+          <t>[ˈkapa] 斗篷；披风；层&lt;名&gt;</t>
         </is>
       </c>
       <c r="C577" s="1" t="inlineStr">
@@ -18821,7 +18877,7 @@
       </c>
       <c r="D577" s="1" t="inlineStr">
         <is>
-          <t>海角</t>
+          <t>斗篷；披风；层</t>
         </is>
       </c>
       <c r="E577" s="1" t="inlineStr">
@@ -19131,13 +19187,17 @@
       </c>
       <c r="B587" s="1" t="inlineStr">
         <is>
-          <t>货车&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C587" s="1" t="inlineStr"/>
+          <t>[[fuɾɣoˈneta]] 厢式小货车&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C587" s="1" t="inlineStr">
+        <is>
+          <t>/fuɾɡoˈneta/</t>
+        </is>
+      </c>
       <c r="D587" s="1" t="inlineStr">
         <is>
-          <t>货车</t>
+          <t>厢式小货车&lt;名&gt;</t>
         </is>
       </c>
       <c r="E587" s="1" t="inlineStr">
@@ -19226,7 +19286,11 @@
           <t>初级&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C590" s="1" t="inlineStr"/>
+      <c r="C590" s="1" t="inlineStr">
+        <is>
+          <t>/xuniˈoɾ/</t>
+        </is>
+      </c>
       <c r="D590" s="1" t="inlineStr">
         <is>
           <t>初级</t>
@@ -19347,7 +19411,7 @@
       </c>
       <c r="B594" s="1" t="inlineStr">
         <is>
-          <t>[ˈklasiko] 经典&lt;名&gt;</t>
+          <t>[/ˈklasiko/] 经典的&lt;形&gt;；经典作品&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C594" s="1" t="inlineStr">
@@ -19357,7 +19421,7 @@
       </c>
       <c r="D594" s="1" t="inlineStr">
         <is>
-          <t>经典</t>
+          <t>经典的&lt;形&gt;；经典作品&lt;名&gt;</t>
         </is>
       </c>
       <c r="E594" s="1" t="inlineStr">
@@ -19379,7 +19443,7 @@
       </c>
       <c r="B595" s="1" t="inlineStr">
         <is>
-          <t>[ˈsake] 服务&lt;名&gt;</t>
+          <t>[/ˈsake/] 发球&lt;名&gt;；（sacar 的虚拟式）取出&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C595" s="1" t="inlineStr">
@@ -19389,7 +19453,7 @@
       </c>
       <c r="D595" s="1" t="inlineStr">
         <is>
-          <t>服务</t>
+          <t>发球&lt;名&gt;；（sacar 的虚拟式）取出&lt;动&gt;</t>
         </is>
       </c>
       <c r="E595" s="1" t="inlineStr">
@@ -19603,7 +19667,7 @@
       </c>
       <c r="B602" s="1" t="inlineStr">
         <is>
-          <t>[oɾdeˈnaɾ] 订单&lt;动&gt;</t>
+          <t>[oɾdeˈnaɾ] 整理；排列；命令&lt;动&gt;</t>
         </is>
       </c>
       <c r="C602" s="1" t="inlineStr">
@@ -19613,7 +19677,7 @@
       </c>
       <c r="D602" s="1" t="inlineStr">
         <is>
-          <t>订单</t>
+          <t>整理；排列；命令</t>
         </is>
       </c>
       <c r="E602" s="1" t="inlineStr">
@@ -19731,7 +19795,7 @@
       </c>
       <c r="B606" s="1" t="inlineStr">
         <is>
-          <t>[ˈxaus] 房子&lt;名&gt;</t>
+          <t>[ˈxaus] 房子；住宅&lt;名&gt;</t>
         </is>
       </c>
       <c r="C606" s="1" t="inlineStr">
@@ -19741,7 +19805,7 @@
       </c>
       <c r="D606" s="1" t="inlineStr">
         <is>
-          <t>房子</t>
+          <t>房子；住宅</t>
         </is>
       </c>
       <c r="E606" s="1" t="inlineStr">
@@ -19859,7 +19923,7 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>[eˈtapa] 舞台&lt;名&gt;</t>
+          <t>[eˈtapa] 阶段；时期&lt;名&gt;</t>
         </is>
       </c>
       <c r="C610" s="1" t="inlineStr">
@@ -19869,7 +19933,7 @@
       </c>
       <c r="D610" s="1" t="inlineStr">
         <is>
-          <t>舞台</t>
+          <t>阶段；时期</t>
         </is>
       </c>
       <c r="E610" s="1" t="inlineStr">
@@ -20243,7 +20307,7 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>[ˈplano] 飞机&lt;名&gt;</t>
+          <t>[ˈplano] 平面；平面图；地图&lt;名&gt;</t>
         </is>
       </c>
       <c r="C622" s="1" t="inlineStr">
@@ -20253,7 +20317,7 @@
       </c>
       <c r="D622" s="1" t="inlineStr">
         <is>
-          <t>飞机</t>
+          <t>平面；平面图；地图</t>
         </is>
       </c>
       <c r="E622" s="1" t="inlineStr">
@@ -20381,7 +20445,7 @@
       </c>
       <c r="D626" s="1" t="inlineStr">
         <is>
-          <t>绿色</t>
+          <t>英语借词，非西班牙语词汇（西语应为 verde）</t>
         </is>
       </c>
       <c r="E626" s="1" t="inlineStr">
@@ -20403,7 +20467,7 @@
       </c>
       <c r="B627" s="1" t="inlineStr">
         <is>
-          <t>[disˈfɾaθ] 服装&lt;名&gt;</t>
+          <t>[disˈfɾaθ] 化装服；伪装&lt;名&gt;</t>
         </is>
       </c>
       <c r="C627" s="1" t="inlineStr">
@@ -20413,7 +20477,7 @@
       </c>
       <c r="D627" s="1" t="inlineStr">
         <is>
-          <t>服装</t>
+          <t>化装服；伪装</t>
         </is>
       </c>
       <c r="E627" s="1" t="inlineStr">
@@ -20694,7 +20758,11 @@
           <t>废话&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C636" s="1" t="inlineStr"/>
+      <c r="C636" s="1" t="inlineStr">
+        <is>
+          <t>/blˈa/</t>
+        </is>
+      </c>
       <c r="D636" s="1" t="inlineStr">
         <is>
           <t>废话</t>
@@ -20943,7 +21011,7 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>[xuˈɡada] 玩&lt;名&gt;</t>
+          <t>[/xuˈɡada/] 一步棋；一次进攻&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C644" s="1" t="inlineStr">
@@ -20953,7 +21021,7 @@
       </c>
       <c r="D644" s="1" t="inlineStr">
         <is>
-          <t>玩</t>
+          <t>一步棋；一次进攻&lt;名&gt;</t>
         </is>
       </c>
       <c r="E644" s="1" t="inlineStr">
@@ -21423,7 +21491,7 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>[maɾˈt͡ʃaɾ] 进行曲&lt;动&gt;</t>
+          <t>[/maɾˈt͡ʃaɾ/] 行进&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C659" s="1" t="inlineStr">
@@ -21433,7 +21501,7 @@
       </c>
       <c r="D659" s="1" t="inlineStr">
         <is>
-          <t>进行曲</t>
+          <t>行进&lt;动&gt;</t>
         </is>
       </c>
       <c r="E659" s="1" t="inlineStr">
@@ -21455,7 +21523,7 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>[loˈɡaɾ] 洛加尔&lt;名&gt;</t>
+          <t>[/loˈɡaɾ/] 地方&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C660" s="1" t="inlineStr">
@@ -21465,7 +21533,7 @@
       </c>
       <c r="D660" s="1" t="inlineStr">
         <is>
-          <t>洛加尔</t>
+          <t>地方&lt;名&gt;</t>
         </is>
       </c>
       <c r="E660" s="1" t="inlineStr">
@@ -21583,7 +21651,7 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>[ˈre] 重新&lt;名&gt;</t>
+          <t>[/ˈre/] 重新&lt;前缀&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C664" s="1" t="inlineStr">
@@ -21593,7 +21661,7 @@
       </c>
       <c r="D664" s="1" t="inlineStr">
         <is>
-          <t>重新</t>
+          <t>重新&lt;前缀&gt;</t>
         </is>
       </c>
       <c r="E664" s="1" t="inlineStr">
@@ -21679,7 +21747,7 @@
       </c>
       <c r="B667" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɾindis] 吐司&lt;名&gt;</t>
+          <t>[/ˈbɾindis/] 祝酒&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C667" s="1" t="inlineStr">
@@ -21689,7 +21757,7 @@
       </c>
       <c r="D667" s="1" t="inlineStr">
         <is>
-          <t>吐司</t>
+          <t>祝酒&lt;名&gt;</t>
         </is>
       </c>
       <c r="E667" s="1" t="inlineStr">
@@ -21711,7 +21779,7 @@
       </c>
       <c r="B668" s="1" t="inlineStr">
         <is>
-          <t>[diˈɾeɡta] 直接&lt;名&gt;</t>
+          <t>[/diˈɾeɡta/] 直接的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C668" s="1" t="inlineStr">
@@ -21721,7 +21789,7 @@
       </c>
       <c r="D668" s="1" t="inlineStr">
         <is>
-          <t>直接</t>
+          <t>直接的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E668" s="1" t="inlineStr">
@@ -22223,7 +22291,7 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>[aˈlibjo] 救济&lt;名&gt;</t>
+          <t>[/aˈlibjo/] 宽慰；缓解&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C684" s="1" t="inlineStr">
@@ -22233,7 +22301,7 @@
       </c>
       <c r="D684" s="1" t="inlineStr">
         <is>
-          <t>救济</t>
+          <t>宽慰；缓解&lt;名&gt;</t>
         </is>
       </c>
       <c r="E684" s="1" t="inlineStr">
@@ -22703,7 +22771,7 @@
       </c>
       <c r="B699" s="1" t="inlineStr">
         <is>
-          <t>[busˈkaɾla] 寻找它&lt;名&gt;</t>
+          <t>[/busˈkaɾla/] 丘鹬&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C699" s="1" t="inlineStr">
@@ -22713,7 +22781,7 @@
       </c>
       <c r="D699" s="1" t="inlineStr">
         <is>
-          <t>寻找它</t>
+          <t>丘鹬</t>
         </is>
       </c>
       <c r="E699" s="1" t="inlineStr">
@@ -22735,7 +22803,7 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>[ˈmona] 可爱&lt;名&gt;</t>
+          <t>[ˈmona] 母猴；雌猴&lt;名&gt;</t>
         </is>
       </c>
       <c r="C700" s="1" t="inlineStr">
@@ -22745,7 +22813,7 @@
       </c>
       <c r="D700" s="1" t="inlineStr">
         <is>
-          <t>可爱</t>
+          <t>母猴；雌猴</t>
         </is>
       </c>
       <c r="E700" s="1" t="inlineStr">
@@ -22799,7 +22867,7 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>[ˈfɾanko] 弗兰克&lt;名&gt;</t>
+          <t>[/ˈfɾanko/] 坦率的&lt;形&gt;；免税的&lt;形&gt;；法兰克人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C702" s="1" t="inlineStr">
@@ -22809,7 +22877,7 @@
       </c>
       <c r="D702" s="1" t="inlineStr">
         <is>
-          <t>弗兰克</t>
+          <t>坦率的&lt;形&gt;；免税的&lt;形&gt;；法兰克人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E702" s="1" t="inlineStr">
@@ -23666,7 +23734,11 @@
           <t>夫人&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C729" s="1" t="inlineStr"/>
+      <c r="C729" s="1" t="inlineStr">
+        <is>
+          <t>/sɾˈa/</t>
+        </is>
+      </c>
       <c r="D729" s="1" t="inlineStr">
         <is>
           <t>夫人</t>
@@ -23883,7 +23955,7 @@
       </c>
       <c r="B736" s="1" t="inlineStr">
         <is>
-          <t>[enfɾenˈtaɾ] 脸&lt;动&gt;</t>
+          <t>[enfɾenˈtaɾ] 使面对；对抗；面临&lt;动&gt;</t>
         </is>
       </c>
       <c r="C736" s="1" t="inlineStr">
@@ -23893,7 +23965,7 @@
       </c>
       <c r="D736" s="1" t="inlineStr">
         <is>
-          <t>脸</t>
+          <t>使面对；对抗；面临</t>
         </is>
       </c>
       <c r="E736" s="1" t="inlineStr">
@@ -24075,7 +24147,7 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>[koˈɾea] 韩国&lt;名&gt;</t>
+          <t>[/koˈɾea/] Corea（韩国，专有名词应大写）；小写 corea 为 corear 的动词变位&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C742" s="1" t="inlineStr">
@@ -24085,7 +24157,7 @@
       </c>
       <c r="D742" s="1" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>Corea（韩国，专有名词应大写）；小写 corea 为 corear 的动词变位</t>
         </is>
       </c>
       <c r="E742" s="1" t="inlineStr">
@@ -24171,7 +24243,7 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>[xuθˈɡaɾ] 法官&lt;动&gt;</t>
+          <t>[xuθˈɡaɾ] 审判；判断；认为&lt;动&gt;</t>
         </is>
       </c>
       <c r="C745" s="1" t="inlineStr">
@@ -24181,7 +24253,7 @@
       </c>
       <c r="D745" s="1" t="inlineStr">
         <is>
-          <t>法官</t>
+          <t>审判；判断；认为</t>
         </is>
       </c>
       <c r="E745" s="1" t="inlineStr">
@@ -24235,7 +24307,7 @@
       </c>
       <c r="B747" s="1" t="inlineStr">
         <is>
-          <t>[ˈmaɾθo] 进行曲&lt;名&gt;</t>
+          <t>[ˈmaɾθo] 三月&lt;名&gt;</t>
         </is>
       </c>
       <c r="C747" s="1" t="inlineStr">
@@ -24245,7 +24317,7 @@
       </c>
       <c r="D747" s="1" t="inlineStr">
         <is>
-          <t>进行曲</t>
+          <t>三月</t>
         </is>
       </c>
       <c r="E747" s="1" t="inlineStr">
@@ -24395,7 +24467,7 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>[ˈbeɾa] 维拉&lt;名&gt;</t>
+          <t>[/ˈbeɾa/] 边缘；边界；旁边&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
@@ -24405,7 +24477,7 @@
       </c>
       <c r="D752" s="1" t="inlineStr">
         <is>
-          <t>维拉</t>
+          <t>边缘；边界；旁边</t>
         </is>
       </c>
       <c r="E752" s="1" t="inlineStr">
@@ -24875,7 +24947,7 @@
       </c>
       <c r="B767" s="1" t="inlineStr">
         <is>
-          <t>[numeˈɾaɾ] 数量&lt;动&gt;</t>
+          <t>[/numeˈɾaɾ/] 编号；计数&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C767" s="1" t="inlineStr">
@@ -24885,7 +24957,7 @@
       </c>
       <c r="D767" s="1" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>编号；计数</t>
         </is>
       </c>
       <c r="E767" s="1" t="inlineStr">
@@ -25035,7 +25107,7 @@
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>[ˈfeɾja] 公平&lt;名&gt;</t>
+          <t>[/ˈfeɾja/] 集市；博览会；游乐场&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C772" s="1" t="inlineStr">
@@ -25045,7 +25117,7 @@
       </c>
       <c r="D772" s="1" t="inlineStr">
         <is>
-          <t>公平</t>
+          <t>集市；博览会；游乐场</t>
         </is>
       </c>
       <c r="E772" s="1" t="inlineStr">
@@ -25579,7 +25651,7 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>[eskoˈlaɾ] 学校&lt;名&gt;</t>
+          <t>[/eskoˈlaɾ/] 学校的；学龄的；学生&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C789" s="1" t="inlineStr">
@@ -25589,7 +25661,7 @@
       </c>
       <c r="D789" s="1" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>学校的；学龄的；学生</t>
         </is>
       </c>
       <c r="E789" s="1" t="inlineStr">
@@ -25675,7 +25747,7 @@
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>[ˈkinto] 第五&lt;名&gt;</t>
+          <t>[/ˈkinto/] 第五的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C792" s="1" t="inlineStr">
@@ -25685,7 +25757,7 @@
       </c>
       <c r="D792" s="1" t="inlineStr">
         <is>
-          <t>第五</t>
+          <t>第五的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E792" s="1" t="inlineStr">
@@ -25963,7 +26035,7 @@
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
-          <t>[medikaˈmento] 医学&lt;名&gt;</t>
+          <t>[/medikaˈmento/] 药物；药品&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C801" s="1" t="inlineStr">
@@ -25973,7 +26045,7 @@
       </c>
       <c r="D801" s="1" t="inlineStr">
         <is>
-          <t>医学</t>
+          <t>药物；药品</t>
         </is>
       </c>
       <c r="E801" s="1" t="inlineStr">
@@ -26059,7 +26131,7 @@
       </c>
       <c r="B804" s="1" t="inlineStr">
         <is>
-          <t>[uˈniɾ] 团结起来&lt;动&gt;</t>
+          <t>[/uˈniɾ/] 联合；连接&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C804" s="1" t="inlineStr">
@@ -26069,7 +26141,7 @@
       </c>
       <c r="D804" s="1" t="inlineStr">
         <is>
-          <t>团结起来</t>
+          <t>联合；连接</t>
         </is>
       </c>
       <c r="E804" s="1" t="inlineStr">
@@ -26283,7 +26355,7 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>[aˈeɾeo] 天线&lt;形&gt;</t>
+          <t>[/aˈeɾeo/] 空中的；航空的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C811" s="1" t="inlineStr">
@@ -26293,7 +26365,7 @@
       </c>
       <c r="D811" s="1" t="inlineStr">
         <is>
-          <t>天线</t>
+          <t>空中的；航空的</t>
         </is>
       </c>
       <c r="E811" s="1" t="inlineStr">
@@ -26635,7 +26707,7 @@
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡota] 掉落&lt;名&gt;</t>
+          <t>[/ˈɡota/] 滴；水滴；痛风&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C822" s="1" t="inlineStr">
@@ -26645,7 +26717,7 @@
       </c>
       <c r="D822" s="1" t="inlineStr">
         <is>
-          <t>掉落</t>
+          <t>滴；水滴；痛风</t>
         </is>
       </c>
       <c r="E822" s="1" t="inlineStr">
@@ -26667,13 +26739,17 @@
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
-          <t>帕&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C823" s="1" t="inlineStr"/>
+          <t>[[pa] 爸爸；爹（papá的口语形式）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C823" s="1" t="inlineStr">
+        <is>
+          <t>/pˈa/</t>
+        </is>
+      </c>
       <c r="D823" s="1" t="inlineStr">
         <is>
-          <t>帕</t>
+          <t>爸爸；爹（papá的口语形式）</t>
         </is>
       </c>
       <c r="E823" s="1" t="inlineStr">
@@ -26759,7 +26835,7 @@
       </c>
       <c r="B826" s="1" t="inlineStr">
         <is>
-          <t>[kontaɡˈtaɾ] 联系方式&lt;动&gt;</t>
+          <t>[/kontaɡˈtaɾ/] 联系；联络&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C826" s="1" t="inlineStr">
@@ -26769,7 +26845,7 @@
       </c>
       <c r="D826" s="1" t="inlineStr">
         <is>
-          <t>联系方式</t>
+          <t>联系；联络</t>
         </is>
       </c>
       <c r="E826" s="1" t="inlineStr">
@@ -26855,7 +26931,7 @@
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
-          <t>[kɾeˈido] 相信&lt;形&gt;</t>
+          <t>[/kɾeˈido/] 自负的；自以为是的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C829" s="1" t="inlineStr">
@@ -26865,7 +26941,7 @@
       </c>
       <c r="D829" s="1" t="inlineStr">
         <is>
-          <t>相信</t>
+          <t>自负的；自以为是的</t>
         </is>
       </c>
       <c r="E829" s="1" t="inlineStr">
@@ -27111,7 +27187,7 @@
       </c>
       <c r="B837" s="1" t="inlineStr">
         <is>
-          <t>[ˈna] 娜&lt;代&gt;</t>
+          <t>[/ˈna/] 无；什么也没有（nada的口语形式）&lt;pron&gt;</t>
         </is>
       </c>
       <c r="C837" s="1" t="inlineStr">
@@ -27121,7 +27197,7 @@
       </c>
       <c r="D837" s="1" t="inlineStr">
         <is>
-          <t>娜</t>
+          <t>无；什么也没有（nada的口语形式）</t>
         </is>
       </c>
       <c r="E837" s="1" t="inlineStr">
@@ -27335,7 +27411,7 @@
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
-          <t>[emˈbio] 运输&lt;名&gt;</t>
+          <t>[/emˈbio/] 运输&lt;名&gt;；寄送的货物&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C844" s="1" t="inlineStr">
@@ -27345,7 +27421,7 @@
       </c>
       <c r="D844" s="1" t="inlineStr">
         <is>
-          <t>运输</t>
+          <t>运输&lt;名&gt;；寄送的货物&lt;名&gt;</t>
         </is>
       </c>
       <c r="E844" s="1" t="inlineStr">
@@ -27527,7 +27603,7 @@
       </c>
       <c r="B850" s="1" t="inlineStr">
         <is>
-          <t>[ˈsalbe] 冰雹&lt;叹&gt;</t>
+          <t>[/ˈsalbe/] 你好；致敬；礼炮&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C850" s="1" t="inlineStr">
@@ -27537,7 +27613,7 @@
       </c>
       <c r="D850" s="1" t="inlineStr">
         <is>
-          <t>冰雹</t>
+          <t>你好；致敬；礼炮</t>
         </is>
       </c>
       <c r="E850" s="1" t="inlineStr">
@@ -27655,7 +27731,7 @@
       </c>
       <c r="B854" s="1" t="inlineStr">
         <is>
-          <t>[foɾtaˈleθa] 实力&lt;名&gt;</t>
+          <t>[/foɾtaˈleθa/] 堡垒&lt;名&gt;；坚强&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C854" s="1" t="inlineStr">
@@ -27665,7 +27741,7 @@
       </c>
       <c r="D854" s="1" t="inlineStr">
         <is>
-          <t>实力</t>
+          <t>堡垒&lt;名&gt;；坚强&lt;名&gt;</t>
         </is>
       </c>
       <c r="E854" s="1" t="inlineStr">
@@ -27975,7 +28051,7 @@
       </c>
       <c r="B864" s="1" t="inlineStr">
         <is>
-          <t>[ˈbo] 博&lt;叹&gt;</t>
+          <t>[/ˈbo/] （唤猪等牲畜的吆喝声）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C864" s="1" t="inlineStr">
@@ -27985,7 +28061,7 @@
       </c>
       <c r="D864" s="1" t="inlineStr">
         <is>
-          <t>博</t>
+          <t>（唤猪等牲畜的吆喝声）</t>
         </is>
       </c>
       <c r="E864" s="1" t="inlineStr">
@@ -28679,7 +28755,7 @@
       </c>
       <c r="B886" s="1" t="inlineStr">
         <is>
-          <t>[ˈbe] 是&lt;名&gt;</t>
+          <t>[/ˈbe/] （西班牙语字母）B的名称&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C886" s="1" t="inlineStr">
@@ -28689,7 +28765,7 @@
       </c>
       <c r="D886" s="1" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>（西班牙语字母）B的名称</t>
         </is>
       </c>
       <c r="E886" s="1" t="inlineStr">
@@ -29959,7 +30035,7 @@
       </c>
       <c r="B926" s="1" t="inlineStr">
         <is>
-          <t>[ˈmaɾxen] 保证金&lt;名&gt;</t>
+          <t>[/ˈmaɾxen/] 边缘；页边空白；河岸；余地&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C926" s="1" t="inlineStr">
@@ -29969,7 +30045,7 @@
       </c>
       <c r="D926" s="1" t="inlineStr">
         <is>
-          <t>保证金</t>
+          <t>边缘；页边空白；河岸；余地</t>
         </is>
       </c>
       <c r="E926" s="1" t="inlineStr">
@@ -30087,7 +30163,7 @@
       </c>
       <c r="B930" s="1" t="inlineStr">
         <is>
-          <t>[konˈswelo] 舒适度&lt;名&gt;</t>
+          <t>[/konˈswelo/] 安慰；慰藉&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C930" s="1" t="inlineStr">
@@ -30097,7 +30173,7 @@
       </c>
       <c r="D930" s="1" t="inlineStr">
         <is>
-          <t>舒适度</t>
+          <t>安慰；慰藉</t>
         </is>
       </c>
       <c r="E930" s="1" t="inlineStr">
@@ -30343,7 +30419,7 @@
       </c>
       <c r="B938" s="1" t="inlineStr">
         <is>
-          <t>[alimenˈtaɾ] 饲料&lt;动&gt;</t>
+          <t>[/alimenˈtaɾ/] 喂养；饲养；供养&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C938" s="1" t="inlineStr">
@@ -30353,7 +30429,7 @@
       </c>
       <c r="D938" s="1" t="inlineStr">
         <is>
-          <t>饲料</t>
+          <t>喂养；饲养；供养</t>
         </is>
       </c>
       <c r="E938" s="1" t="inlineStr">
@@ -30471,7 +30547,7 @@
       </c>
       <c r="B942" s="1" t="inlineStr">
         <is>
-          <t>[fakulˈtad] 师资队伍&lt;名&gt;</t>
+          <t>[/fakulˈtad/] 能力；才能；（大学）院系&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C942" s="1" t="inlineStr">
@@ -30481,7 +30557,7 @@
       </c>
       <c r="D942" s="1" t="inlineStr">
         <is>
-          <t>师资队伍</t>
+          <t>能力；才能；（大学）院系</t>
         </is>
       </c>
       <c r="E942" s="1" t="inlineStr">
@@ -30823,7 +30899,7 @@
       </c>
       <c r="B953" s="1" t="inlineStr">
         <is>
-          <t>[koˈreos] 电子邮件&lt;名&gt;</t>
+          <t>[/koˈreos/] 邮政；邮件&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C953" s="1" t="inlineStr">
@@ -30833,7 +30909,7 @@
       </c>
       <c r="D953" s="1" t="inlineStr">
         <is>
-          <t>电子邮件</t>
+          <t>邮政；邮件</t>
         </is>
       </c>
       <c r="E953" s="1" t="inlineStr">
@@ -30919,7 +30995,7 @@
       </c>
       <c r="B956" s="1" t="inlineStr">
         <is>
-          <t>[iˈniθjo] 家&lt;名&gt;</t>
+          <t>[/iˈniθjo/] 开始；开端&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C956" s="1" t="inlineStr">
@@ -30929,7 +31005,7 @@
       </c>
       <c r="D956" s="1" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>开始；开端</t>
         </is>
       </c>
       <c r="E956" s="1" t="inlineStr">
@@ -31239,7 +31315,7 @@
       </c>
       <c r="B966" s="1" t="inlineStr">
         <is>
-          <t>[ˈbako] 空的&lt;名&gt;</t>
+          <t>[/ˈbako/] （西语中无此词，应为 vacío）空的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C966" s="1" t="inlineStr">
@@ -31249,7 +31325,7 @@
       </c>
       <c r="D966" s="1" t="inlineStr">
         <is>
-          <t>空的</t>
+          <t>（西语中无此词，应为 vacío）空的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E966" s="1" t="inlineStr">
@@ -32039,7 +32115,7 @@
       </c>
       <c r="B991" s="1" t="inlineStr">
         <is>
-          <t>[enθenˈdido] 上&lt;名&gt;</t>
+          <t>[/enθenˈdido/] 点火；点燃；开启&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C991" s="1" t="inlineStr">
@@ -32049,7 +32125,7 @@
       </c>
       <c r="D991" s="1" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>点火；点燃；开启</t>
         </is>
       </c>
       <c r="E991" s="1" t="inlineStr">
@@ -32327,7 +32403,7 @@
       </c>
       <c r="B1000" s="1" t="inlineStr">
         <is>
-          <t>[pɾesenˈtado] 提出&lt;形&gt;</t>
+          <t>[/pɾesenˈtado/] 介绍；提交（presentar 的过去分词）&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1000" s="1" t="inlineStr">
@@ -32337,7 +32413,7 @@
       </c>
       <c r="D1000" s="1" t="inlineStr">
         <is>
-          <t>提出</t>
+          <t>介绍；提交（presentar 的过去分词）</t>
         </is>
       </c>
       <c r="E1000" s="1" t="inlineStr">
@@ -32362,7 +32438,11 @@
           <t>基于&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1001" s="1" t="inlineStr"/>
+      <c r="C1001" s="1" t="inlineStr">
+        <is>
+          <t>/baˈsaðo/</t>
+        </is>
+      </c>
       <c r="D1001" s="1" t="inlineStr">
         <is>
           <t>基于</t>
@@ -32931,7 +33011,7 @@
       </c>
       <c r="B1019" s="1" t="inlineStr">
         <is>
-          <t>[siˈkopata] 精神病患者&lt;名&gt;</t>
+          <t>[/siˈkopata/] 精神变态者；反社会人格者&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1019" s="1" t="inlineStr">
@@ -32941,7 +33021,7 @@
       </c>
       <c r="D1019" s="1" t="inlineStr">
         <is>
-          <t>精神病患者</t>
+          <t>精神变态者；反社会人格者</t>
         </is>
       </c>
       <c r="E1019" s="1" t="inlineStr">
@@ -33187,7 +33267,7 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>[aθeɾˈkaɾ] 放大&lt;动&gt;</t>
+          <t>[/aθeɾˈkaɾ/] 使靠近；使接近&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1027" s="1" t="inlineStr">
@@ -33197,7 +33277,7 @@
       </c>
       <c r="D1027" s="1" t="inlineStr">
         <is>
-          <t>放大</t>
+          <t>使靠近；使接近</t>
         </is>
       </c>
       <c r="E1027" s="1" t="inlineStr">
@@ -33283,7 +33363,7 @@
       </c>
       <c r="B1030" s="1" t="inlineStr">
         <is>
-          <t>[ˈteme] 恐惧&lt;名&gt;</t>
+          <t>[/ˈteme/] 害怕；恐惧&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1030" s="1" t="inlineStr">
@@ -33293,7 +33373,7 @@
       </c>
       <c r="D1030" s="1" t="inlineStr">
         <is>
-          <t>恐惧</t>
+          <t>害怕；恐惧</t>
         </is>
       </c>
       <c r="E1030" s="1" t="inlineStr">
@@ -33795,7 +33875,7 @@
       </c>
       <c r="B1046" s="1" t="inlineStr">
         <is>
-          <t>[ˈtabla] 表&lt;名&gt;</t>
+          <t>[/ˈtabla/] 木板；板；表格&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1046" s="1" t="inlineStr">
@@ -33805,7 +33885,7 @@
       </c>
       <c r="D1046" s="1" t="inlineStr">
         <is>
-          <t>表</t>
+          <t>木板；板；表格</t>
         </is>
       </c>
       <c r="E1046" s="1" t="inlineStr">
@@ -33859,7 +33939,7 @@
       </c>
       <c r="B1048" s="1" t="inlineStr">
         <is>
-          <t>[baˈɲeɾo] 浴缸&lt;名&gt;</t>
+          <t>[/baˈɲeɾo/] 救生员；浴场服务员&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1048" s="1" t="inlineStr">
@@ -33869,7 +33949,7 @@
       </c>
       <c r="D1048" s="1" t="inlineStr">
         <is>
-          <t>浴缸</t>
+          <t>救生员；浴场服务员</t>
         </is>
       </c>
       <c r="E1048" s="1" t="inlineStr">
@@ -34307,7 +34387,7 @@
       </c>
       <c r="B1062" s="1" t="inlineStr">
         <is>
-          <t>[ˈkoka] 可乐&lt;名&gt;</t>
+          <t>[/ˈkoka/] 古柯（植物）；可卡因&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1062" s="1" t="inlineStr">
@@ -34317,7 +34397,7 @@
       </c>
       <c r="D1062" s="1" t="inlineStr">
         <is>
-          <t>可乐</t>
+          <t>古柯（植物）；可卡因&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1062" s="1" t="inlineStr">
@@ -34499,7 +34579,7 @@
       </c>
       <c r="B1068" s="1" t="inlineStr">
         <is>
-          <t>[ateriˈθaɾ] 土地&lt;动&gt;</t>
+          <t>[/ateriˈθaɾ/] 着陆；降落&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1068" s="1" t="inlineStr">
@@ -34509,7 +34589,7 @@
       </c>
       <c r="D1068" s="1" t="inlineStr">
         <is>
-          <t>土地</t>
+          <t>着陆；降落</t>
         </is>
       </c>
       <c r="E1068" s="1" t="inlineStr">
@@ -34787,7 +34867,7 @@
       </c>
       <c r="B1077" s="1" t="inlineStr">
         <is>
-          <t>[rastɾeˈaɾ] 轨道&lt;动&gt;</t>
+          <t>[/rastɾeˈaɾ/] 追踪；跟踪&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1077" s="1" t="inlineStr">
@@ -34797,7 +34877,7 @@
       </c>
       <c r="D1077" s="1" t="inlineStr">
         <is>
-          <t>轨道</t>
+          <t>追踪；跟踪</t>
         </is>
       </c>
       <c r="E1077" s="1" t="inlineStr">
@@ -34979,13 +35059,17 @@
       </c>
       <c r="B1083" s="1" t="inlineStr">
         <is>
-          <t>锯&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C1083" s="1" t="inlineStr"/>
+          <t>[[ˈbjo] 看见；看到&lt;verb&gt;</t>
+        </is>
+      </c>
+      <c r="C1083" s="1" t="inlineStr">
+        <is>
+          <t>/biˈo/</t>
+        </is>
+      </c>
       <c r="D1083" s="1" t="inlineStr">
         <is>
-          <t>锯</t>
+          <t>看见；看到</t>
         </is>
       </c>
       <c r="E1083" s="1" t="inlineStr">
@@ -35135,7 +35219,7 @@
       </c>
       <c r="B1088" s="1" t="inlineStr">
         <is>
-          <t>[leˈbante] 电梯&lt;名&gt;</t>
+          <t>[/leˈbante/] 东方；东风；升起&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1088" s="1" t="inlineStr">
@@ -35145,7 +35229,7 @@
       </c>
       <c r="D1088" s="1" t="inlineStr">
         <is>
-          <t>电梯</t>
+          <t>东方；东风；升起</t>
         </is>
       </c>
       <c r="E1088" s="1" t="inlineStr">
@@ -35199,7 +35283,7 @@
       </c>
       <c r="B1090" s="1" t="inlineStr">
         <is>
-          <t>[ˈlanθe] 扔&lt;名&gt;</t>
+          <t>[/ˈlanθe/] 意外事件；投掷&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1090" s="1" t="inlineStr">
@@ -35209,7 +35293,7 @@
       </c>
       <c r="D1090" s="1" t="inlineStr">
         <is>
-          <t>扔</t>
+          <t>意外事件；投掷</t>
         </is>
       </c>
       <c r="E1090" s="1" t="inlineStr">
@@ -35711,13 +35795,17 @@
       </c>
       <c r="B1106" s="1" t="inlineStr">
         <is>
-          <t>可能&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1106" s="1" t="inlineStr"/>
+          <t>[[maj] 五月&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1106" s="1" t="inlineStr">
+        <is>
+          <t>/mˈaj/</t>
+        </is>
+      </c>
       <c r="D1106" s="1" t="inlineStr">
         <is>
-          <t>可能</t>
+          <t>五月</t>
         </is>
       </c>
       <c r="E1106" s="1" t="inlineStr">
@@ -36190,7 +36278,11 @@
           <t>基因&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1121" s="1" t="inlineStr"/>
+      <c r="C1121" s="1" t="inlineStr">
+        <is>
+          <t>/xˈene/</t>
+        </is>
+      </c>
       <c r="D1121" s="1" t="inlineStr">
         <is>
           <t>基因</t>
@@ -36442,7 +36534,11 @@
           <t>切&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C1129" s="1" t="inlineStr"/>
+      <c r="C1129" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkoɾten/</t>
+        </is>
+      </c>
       <c r="D1129" s="1" t="inlineStr">
         <is>
           <t>切</t>
@@ -36566,7 +36662,11 @@
           <t>生存&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1133" s="1" t="inlineStr"/>
+      <c r="C1133" s="1" t="inlineStr">
+        <is>
+          <t>/supeɾiˈβenθja/</t>
+        </is>
+      </c>
       <c r="D1133" s="1" t="inlineStr">
         <is>
           <t>生存</t>
@@ -36591,7 +36691,7 @@
       </c>
       <c r="B1134" s="1" t="inlineStr">
         <is>
-          <t>[ˈkan] 可以&lt;名&gt;</t>
+          <t>[/ˈkan/] 罐头；罐子；容器&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1134" s="1" t="inlineStr">
@@ -36601,7 +36701,7 @@
       </c>
       <c r="D1134" s="1" t="inlineStr">
         <is>
-          <t>可以</t>
+          <t>罐头；罐子；容器</t>
         </is>
       </c>
       <c r="E1134" s="1" t="inlineStr">
@@ -37071,13 +37171,17 @@
       </c>
       <c r="B1149" s="1" t="inlineStr">
         <is>
-          <t>坐标&lt;形&gt;</t>
-        </is>
-      </c>
-      <c r="C1149" s="1" t="inlineStr"/>
+          <t>[[kooɾðeˈnaðo]] coordinado 协调的；妥当的&lt;形&gt;&lt;adj&gt;</t>
+        </is>
+      </c>
+      <c r="C1149" s="1" t="inlineStr">
+        <is>
+          <t>/ko.oɾðeˈnaðo/</t>
+        </is>
+      </c>
       <c r="D1149" s="1" t="inlineStr">
         <is>
-          <t>坐标</t>
+          <t>coordinado 协调的；妥当的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1149" s="1" t="inlineStr">
@@ -37323,7 +37427,7 @@
       </c>
       <c r="B1157" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃan] 陈&lt;名&gt;</t>
+          <t>[/ˈt͡ʃan/] 陈（姓氏）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1157" s="1" t="inlineStr">
@@ -37333,7 +37437,7 @@
       </c>
       <c r="D1157" s="1" t="inlineStr">
         <is>
-          <t>陈</t>
+          <t>陈（姓氏）</t>
         </is>
       </c>
       <c r="E1157" s="1" t="inlineStr">
@@ -37707,13 +37811,17 @@
       </c>
       <c r="B1169" s="1" t="inlineStr">
         <is>
+          <t>[[raˈθon]] 原因&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1169" s="1" t="inlineStr">
+        <is>
+          <t>/ɾˈaθon/</t>
+        </is>
+      </c>
+      <c r="D1169" s="1" t="inlineStr">
+        <is>
           <t>原因&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1169" s="1" t="inlineStr"/>
-      <c r="D1169" s="1" t="inlineStr">
-        <is>
-          <t>原因</t>
         </is>
       </c>
       <c r="E1169" s="1" t="inlineStr">
@@ -38055,7 +38163,7 @@
       </c>
       <c r="B1180" s="1" t="inlineStr">
         <is>
-          <t>[asˈθenso] 促销&lt;名&gt;</t>
+          <t>[/asˈθenso/] 晋升；提升；上升&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1180" s="1" t="inlineStr">
@@ -38065,7 +38173,7 @@
       </c>
       <c r="D1180" s="1" t="inlineStr">
         <is>
-          <t>促销</t>
+          <t>晋升；提升；上升</t>
         </is>
       </c>
       <c r="E1180" s="1" t="inlineStr">
@@ -38247,7 +38355,7 @@
       </c>
       <c r="B1186" s="1" t="inlineStr">
         <is>
-          <t>[abanˈθaɾ] 提前&lt;动&gt;</t>
+          <t>[/abanˈθaɾ/] 前进；推进；进展&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1186" s="1" t="inlineStr">
@@ -38257,7 +38365,7 @@
       </c>
       <c r="D1186" s="1" t="inlineStr">
         <is>
-          <t>提前</t>
+          <t>前进；推进；进展</t>
         </is>
       </c>
       <c r="E1186" s="1" t="inlineStr">
@@ -38378,7 +38486,11 @@
           <t>d.&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1190" s="1" t="inlineStr"/>
+      <c r="C1190" s="1" t="inlineStr">
+        <is>
+          <t>/doɡˈtoɾ/</t>
+        </is>
+      </c>
       <c r="D1190" s="1" t="inlineStr">
         <is>
           <t>d.</t>
@@ -38435,7 +38547,7 @@
       </c>
       <c r="B1192" s="1" t="inlineStr">
         <is>
-          <t>[reˈbelde] 叛逆者&lt;名&gt;</t>
+          <t>[/reˈbelde/] 叛逆的&lt;形&gt;；叛逆者&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1192" s="1" t="inlineStr">
@@ -38445,7 +38557,7 @@
       </c>
       <c r="D1192" s="1" t="inlineStr">
         <is>
-          <t>叛逆者</t>
+          <t>叛逆的&lt;形&gt;；叛逆者&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1192" s="1" t="inlineStr">
@@ -39043,7 +39155,7 @@
       </c>
       <c r="B1211" s="1" t="inlineStr">
         <is>
-          <t>[ˈmulta] 很好&lt;名&gt;</t>
+          <t>[/ˈmulta/] 罚款；罚金&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1211" s="1" t="inlineStr">
@@ -39053,7 +39165,7 @@
       </c>
       <c r="D1211" s="1" t="inlineStr">
         <is>
-          <t>很好</t>
+          <t>罚款；罚金</t>
         </is>
       </c>
       <c r="E1211" s="1" t="inlineStr">
@@ -39171,7 +39283,7 @@
       </c>
       <c r="B1215" s="1" t="inlineStr">
         <is>
-          <t>[ˈmisa] 质量&lt;名&gt;</t>
+          <t>[/ˈmisa/] 弥撒&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1215" s="1" t="inlineStr">
@@ -39181,7 +39293,7 @@
       </c>
       <c r="D1215" s="1" t="inlineStr">
         <is>
-          <t>质量</t>
+          <t>弥撒</t>
         </is>
       </c>
       <c r="E1215" s="1" t="inlineStr">
@@ -39299,7 +39411,7 @@
       </c>
       <c r="B1219" s="1" t="inlineStr">
         <is>
-          <t>[ˈida] 一种方式&lt;名&gt;</t>
+          <t>[/ˈida/] 去程；出发；单程&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1219" s="1" t="inlineStr">
@@ -39309,7 +39421,7 @@
       </c>
       <c r="D1219" s="1" t="inlineStr">
         <is>
-          <t>一种方式</t>
+          <t>去程；出发；单程</t>
         </is>
       </c>
       <c r="E1219" s="1" t="inlineStr">
@@ -39427,7 +39539,7 @@
       </c>
       <c r="B1223" s="1" t="inlineStr">
         <is>
-          <t>[puˈɲado] 少数&lt;名&gt;</t>
+          <t>[/puˈɲado/] 一把；少量&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1223" s="1" t="inlineStr">
@@ -39437,7 +39549,7 @@
       </c>
       <c r="D1223" s="1" t="inlineStr">
         <is>
-          <t>少数</t>
+          <t>一把；少量&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1223" s="1" t="inlineStr">
@@ -39491,7 +39603,7 @@
       </c>
       <c r="B1225" s="1" t="inlineStr">
         <is>
-          <t>[liˈxeɾo] 光&lt;形&gt;</t>
+          <t>[/liˈxeɾo/] 轻的；轻便的；轻快的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1225" s="1" t="inlineStr">
@@ -39501,7 +39613,7 @@
       </c>
       <c r="D1225" s="1" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>轻的；轻便的；轻快的</t>
         </is>
       </c>
       <c r="E1225" s="1" t="inlineStr">
@@ -39523,7 +39635,7 @@
       </c>
       <c r="B1226" s="1" t="inlineStr">
         <is>
-          <t>[ˈpeɡa] 击中&lt;名&gt;</t>
+          <t>[/ˈpeɡa/] 缺点；麻烦&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1226" s="1" t="inlineStr">
@@ -39533,7 +39645,7 @@
       </c>
       <c r="D1226" s="1" t="inlineStr">
         <is>
-          <t>击中</t>
+          <t>缺点；麻烦&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1226" s="1" t="inlineStr">
@@ -39683,7 +39795,7 @@
       </c>
       <c r="B1231" s="1" t="inlineStr">
         <is>
-          <t>[ˈsoɾdo] 聋子&lt;名&gt;</t>
+          <t>[/ˈsoɾdo/] 聋的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1231" s="1" t="inlineStr">
@@ -39693,7 +39805,7 @@
       </c>
       <c r="D1231" s="1" t="inlineStr">
         <is>
-          <t>聋子</t>
+          <t>聋的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1231" s="1" t="inlineStr">
@@ -39779,7 +39891,7 @@
       </c>
       <c r="B1234" s="1" t="inlineStr">
         <is>
-          <t>[ˈpila] 堆栈&lt;名&gt;</t>
+          <t>[/ˈpila/] 堆；电池&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1234" s="1" t="inlineStr">
@@ -39789,7 +39901,7 @@
       </c>
       <c r="D1234" s="1" t="inlineStr">
         <is>
-          <t>堆栈</t>
+          <t>堆；电池&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1234" s="1" t="inlineStr">
@@ -39843,7 +39955,7 @@
       </c>
       <c r="B1236" s="1" t="inlineStr">
         <is>
-          <t>[lesˈbjano] 女同性恋&lt;名&gt;</t>
+          <t>[/lesˈbjano/] 女同性恋&lt;名&gt;；女同性恋的&lt;形&gt;（标准形式为 lesbiana）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1236" s="1" t="inlineStr">
@@ -39853,7 +39965,7 @@
       </c>
       <c r="D1236" s="1" t="inlineStr">
         <is>
-          <t>女同性恋</t>
+          <t>女同性恋&lt;名&gt;；女同性恋的&lt;形&gt;（标准形式为 lesbiana）</t>
         </is>
       </c>
       <c r="E1236" s="1" t="inlineStr">
@@ -40195,7 +40307,7 @@
       </c>
       <c r="B1247" s="1" t="inlineStr">
         <is>
-          <t>[koinθiˈdiɾ] 比赛&lt;动&gt;</t>
+          <t>[/koinθiˈdiɾ/] 巧合；一致；相符&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1247" s="1" t="inlineStr">
@@ -40205,7 +40317,7 @@
       </c>
       <c r="D1247" s="1" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>巧合；一致；相符</t>
         </is>
       </c>
       <c r="E1247" s="1" t="inlineStr">
@@ -41123,7 +41235,7 @@
       </c>
       <c r="B1276" s="1" t="inlineStr">
         <is>
-          <t>[entɾeˈnaɾ] 火车&lt;动&gt;</t>
+          <t>[/entɾeˈnaɾ/] 训练；锻炼&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1276" s="1" t="inlineStr">
@@ -41133,7 +41245,7 @@
       </c>
       <c r="D1276" s="1" t="inlineStr">
         <is>
-          <t>火车</t>
+          <t>训练；锻炼</t>
         </is>
       </c>
       <c r="E1276" s="1" t="inlineStr">
@@ -41603,7 +41715,7 @@
       </c>
       <c r="B1291" s="1" t="inlineStr">
         <is>
-          <t>[doˈɾado] 金色&lt;名&gt;</t>
+          <t>[/doˈɾado/] 金色的&lt;形&gt;；镀金的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1291" s="1" t="inlineStr">
@@ -41613,7 +41725,7 @@
       </c>
       <c r="D1291" s="1" t="inlineStr">
         <is>
-          <t>金色</t>
+          <t>金色的&lt;形&gt;；镀金的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1291" s="1" t="inlineStr">
@@ -42019,7 +42131,7 @@
       </c>
       <c r="B1304" s="1" t="inlineStr">
         <is>
-          <t>[rekoˈrido] 游览&lt;名&gt;</t>
+          <t>[/rekoˈrido/] 路线&lt;名&gt;；行程&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1304" s="1" t="inlineStr">
@@ -42029,7 +42141,7 @@
       </c>
       <c r="D1304" s="1" t="inlineStr">
         <is>
-          <t>游览</t>
+          <t>路线&lt;名&gt;；行程&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1304" s="1" t="inlineStr">
@@ -42118,7 +42230,11 @@
           <t>下午&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1307" s="1" t="inlineStr"/>
+      <c r="C1307" s="1" t="inlineStr">
+        <is>
+          <t>/pm/</t>
+        </is>
+      </c>
       <c r="D1307" s="1" t="inlineStr">
         <is>
           <t>下午</t>
@@ -42623,7 +42739,7 @@
       </c>
       <c r="B1323" s="1" t="inlineStr">
         <is>
-          <t>[indiˈbidwo] 个人的&lt;名&gt;</t>
+          <t>[/indiˈbidwo/] 个人；个体&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1323" s="1" t="inlineStr">
@@ -42633,7 +42749,7 @@
       </c>
       <c r="D1323" s="1" t="inlineStr">
         <is>
-          <t>个人的</t>
+          <t>个人；个体</t>
         </is>
       </c>
       <c r="E1323" s="1" t="inlineStr">
@@ -42783,7 +42899,7 @@
       </c>
       <c r="B1328" s="1" t="inlineStr">
         <is>
-          <t>[menˈtaɾ] 薄荷&lt;动&gt;</t>
+          <t>[/menˈtaɾ/] 提及；提到&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1328" s="1" t="inlineStr">
@@ -42793,7 +42909,7 @@
       </c>
       <c r="D1328" s="1" t="inlineStr">
         <is>
-          <t>薄荷</t>
+          <t>提及；提到</t>
         </is>
       </c>
       <c r="E1328" s="1" t="inlineStr">
@@ -42879,7 +42995,7 @@
       </c>
       <c r="B1331" s="1" t="inlineStr">
         <is>
-          <t>[ˈkumple] 遇见&lt;名&gt;</t>
+          <t>[/ˈkumple/] &lt;cumplir 的陈述式现在时第三人称单数&gt;完成&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1331" s="1" t="inlineStr">
@@ -42889,7 +43005,7 @@
       </c>
       <c r="D1331" s="1" t="inlineStr">
         <is>
-          <t>遇见</t>
+          <t>&lt;cumplir 的陈述式现在时第三人称单数&gt;完成&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1331" s="1" t="inlineStr">
@@ -43263,7 +43379,7 @@
       </c>
       <c r="B1343" s="1" t="inlineStr">
         <is>
-          <t>[ˈsabana] 片材&lt;名&gt;</t>
+          <t>[/ˈsabana/] 床单&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1343" s="1" t="inlineStr">
@@ -43273,7 +43389,7 @@
       </c>
       <c r="D1343" s="1" t="inlineStr">
         <is>
-          <t>片材</t>
+          <t>床单</t>
         </is>
       </c>
       <c r="E1343" s="1" t="inlineStr">
@@ -43327,7 +43443,7 @@
       </c>
       <c r="B1345" s="1" t="inlineStr">
         <is>
-          <t>[ˈsip] 是的&lt;叹&gt;</t>
+          <t>[/ˈsip/] 是的（口语）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C1345" s="1" t="inlineStr">
@@ -43337,7 +43453,7 @@
       </c>
       <c r="D1345" s="1" t="inlineStr">
         <is>
-          <t>是的</t>
+          <t>是的（口语）</t>
         </is>
       </c>
       <c r="E1345" s="1" t="inlineStr">
@@ -43679,7 +43795,7 @@
       </c>
       <c r="B1356" s="1" t="inlineStr">
         <is>
-          <t>[kabtuˈɾaɾ] 捕获&lt;动&gt;</t>
+          <t>[/kabtuˈɾaɾ/] 捕获&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1356" s="1" t="inlineStr">
@@ -43689,7 +43805,7 @@
       </c>
       <c r="D1356" s="1" t="inlineStr">
         <is>
-          <t>捕获</t>
+          <t>捕获&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1356" s="1" t="inlineStr">
@@ -43711,7 +43827,7 @@
       </c>
       <c r="B1357" s="1" t="inlineStr">
         <is>
-          <t>[kuˈɲado] 妹夫&lt;名&gt;</t>
+          <t>[/kuˈɲado/] 姐夫，妹夫（配偶的兄弟，或姐妹的丈夫）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1357" s="1" t="inlineStr">
@@ -43721,7 +43837,7 @@
       </c>
       <c r="D1357" s="1" t="inlineStr">
         <is>
-          <t>妹夫</t>
+          <t>姐夫，妹夫（配偶的兄弟，或姐妹的丈夫）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1357" s="1" t="inlineStr">
@@ -43903,7 +44019,7 @@
       </c>
       <c r="B1363" s="1" t="inlineStr">
         <is>
-          <t>[fiɡˈθjon] 小说&lt;名&gt;</t>
+          <t>[/fiɡˈθjon/] 虚构，幻想；虚构作品&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1363" s="1" t="inlineStr">
@@ -43913,7 +44029,7 @@
       </c>
       <c r="D1363" s="1" t="inlineStr">
         <is>
-          <t>小说</t>
+          <t>虚构，幻想；虚构作品&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1363" s="1" t="inlineStr">
@@ -43935,13 +44051,17 @@
       </c>
       <c r="B1364" s="1" t="inlineStr">
         <is>
-          <t>我去了&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C1364" s="1" t="inlineStr"/>
+          <t>[[ˈfwi]] fui 我去了&lt;动&gt;&lt;verb&gt;</t>
+        </is>
+      </c>
+      <c r="C1364" s="1" t="inlineStr">
+        <is>
+          <t>/fuˈi/</t>
+        </is>
+      </c>
       <c r="D1364" s="1" t="inlineStr">
         <is>
-          <t>我去了</t>
+          <t>fui 我去了&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1364" s="1" t="inlineStr">
@@ -44091,7 +44211,7 @@
       </c>
       <c r="B1369" s="1" t="inlineStr">
         <is>
-          <t>[doˈθeno] 十几个&lt;形&gt;</t>
+          <t>[/doˈθeno/] 一打的；十二个一组的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1369" s="1" t="inlineStr">
@@ -44101,7 +44221,7 @@
       </c>
       <c r="D1369" s="1" t="inlineStr">
         <is>
-          <t>十几个</t>
+          <t>一打的；十二个一组的</t>
         </is>
       </c>
       <c r="E1369" s="1" t="inlineStr">
@@ -44510,7 +44630,11 @@
           <t>向上&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1382" s="1" t="inlineStr"/>
+      <c r="C1382" s="1" t="inlineStr">
+        <is>
+          <t>/ˈup/</t>
+        </is>
+      </c>
       <c r="D1382" s="1" t="inlineStr">
         <is>
           <t>向上</t>
@@ -44823,7 +44947,7 @@
       </c>
       <c r="B1392" s="1" t="inlineStr">
         <is>
-          <t>[ˈpolis] 警察&lt;名&gt;</t>
+          <t>[/ˈpolis/] 城邦&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1392" s="1" t="inlineStr">
@@ -44833,7 +44957,7 @@
       </c>
       <c r="D1392" s="1" t="inlineStr">
         <is>
-          <t>警察</t>
+          <t>城邦</t>
         </is>
       </c>
       <c r="E1392" s="1" t="inlineStr">
@@ -45143,7 +45267,7 @@
       </c>
       <c r="B1402" s="1" t="inlineStr">
         <is>
-          <t>[ˈbit͡ʃo] 错误&lt;名&gt;</t>
+          <t>[/ˈbit͡ʃo/] 虫子；小动物&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1402" s="1" t="inlineStr">
@@ -45153,7 +45277,7 @@
       </c>
       <c r="D1402" s="1" t="inlineStr">
         <is>
-          <t>错误</t>
+          <t>虫子；小动物</t>
         </is>
       </c>
       <c r="E1402" s="1" t="inlineStr">
@@ -46679,7 +46803,7 @@
       </c>
       <c r="B1450" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɾjaɾ] 提高&lt;动&gt;</t>
+          <t>[/ˈkɾjaɾ/] 抚养；饲养；培育&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1450" s="1" t="inlineStr">
@@ -46689,7 +46813,7 @@
       </c>
       <c r="D1450" s="1" t="inlineStr">
         <is>
-          <t>提高</t>
+          <t>抚养；饲养；培育</t>
         </is>
       </c>
       <c r="E1450" s="1" t="inlineStr">
@@ -46711,7 +46835,7 @@
       </c>
       <c r="B1451" s="1" t="inlineStr">
         <is>
-          <t>[koloˈkaɾ] 地方&lt;动&gt;</t>
+          <t>[/koloˈkaɾ/] 放置；安放；安置&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1451" s="1" t="inlineStr">
@@ -46721,7 +46845,7 @@
       </c>
       <c r="D1451" s="1" t="inlineStr">
         <is>
-          <t>地方</t>
+          <t>放置；安放；安置</t>
         </is>
       </c>
       <c r="E1451" s="1" t="inlineStr">
@@ -46871,10 +46995,14 @@
       </c>
       <c r="B1456" s="1" t="inlineStr">
         <is>
-          <t>东&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1456" s="1" t="inlineStr"/>
+          <t>[[doŋ] 东&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1456" s="1" t="inlineStr">
+        <is>
+          <t>/dˈonx/</t>
+        </is>
+      </c>
       <c r="D1456" s="1" t="inlineStr">
         <is>
           <t>东</t>
@@ -47443,7 +47571,7 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>[filˈmaɾ] 电影&lt;动&gt;</t>
+          <t>[/filˈmaɾ/] 拍摄；摄制&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1474" s="1" t="inlineStr">
@@ -47453,7 +47581,7 @@
       </c>
       <c r="D1474" s="1" t="inlineStr">
         <is>
-          <t>电影</t>
+          <t>拍摄；摄制</t>
         </is>
       </c>
       <c r="E1474" s="1" t="inlineStr">
@@ -47507,7 +47635,7 @@
       </c>
       <c r="B1476" s="1" t="inlineStr">
         <is>
-          <t>[ˈmoska] 飞&lt;名&gt;</t>
+          <t>[/ˈmoska/] 苍蝇&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1476" s="1" t="inlineStr">
@@ -47517,7 +47645,7 @@
       </c>
       <c r="D1476" s="1" t="inlineStr">
         <is>
-          <t>飞</t>
+          <t>苍蝇</t>
         </is>
       </c>
       <c r="E1476" s="1" t="inlineStr">
@@ -47603,7 +47731,7 @@
       </c>
       <c r="B1479" s="1" t="inlineStr">
         <is>
-          <t>[ˈrama] 分行&lt;名&gt;</t>
+          <t>[/ˈrama/] 树枝；枝&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1479" s="1" t="inlineStr">
@@ -47613,7 +47741,7 @@
       </c>
       <c r="D1479" s="1" t="inlineStr">
         <is>
-          <t>分行</t>
+          <t>树枝；枝</t>
         </is>
       </c>
       <c r="E1479" s="1" t="inlineStr">
@@ -48659,13 +48787,17 @@
       </c>
       <c r="B1512" s="1" t="inlineStr">
         <is>
-          <t>想念&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1512" s="1" t="inlineStr"/>
+          <t>[[ˈese aˈerre ˈte aˈkento] 小姐&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1512" s="1" t="inlineStr">
+        <is>
+          <t>/seɲoɾita/</t>
+        </is>
+      </c>
       <c r="D1512" s="1" t="inlineStr">
         <is>
-          <t>想念</t>
+          <t>小姐</t>
         </is>
       </c>
       <c r="E1512" s="1" t="inlineStr">
@@ -48754,7 +48886,11 @@
           <t>赢了&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1515" s="1" t="inlineStr"/>
+      <c r="C1515" s="1" t="inlineStr">
+        <is>
+          <t>/wˈon/</t>
+        </is>
+      </c>
       <c r="D1515" s="1" t="inlineStr">
         <is>
           <t>赢了</t>
@@ -48875,7 +49011,7 @@
       </c>
       <c r="B1519" s="1" t="inlineStr">
         <is>
-          <t>[pɾefeˈɾido] 首选&lt;名&gt;</t>
+          <t>[/pɾefeˈɾido/] 首选的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1519" s="1" t="inlineStr">
@@ -48885,7 +49021,7 @@
       </c>
       <c r="D1519" s="1" t="inlineStr">
         <is>
-          <t>首选</t>
+          <t>首选的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1519" s="1" t="inlineStr">
@@ -49515,7 +49651,7 @@
       </c>
       <c r="B1539" s="1" t="inlineStr">
         <is>
-          <t>[eɡspɾeˈsaɾ] 快递&lt;动&gt;</t>
+          <t>[/eɡspɾeˈsaɾ/] 表达；表示&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1539" s="1" t="inlineStr">
@@ -49525,7 +49661,7 @@
       </c>
       <c r="D1539" s="1" t="inlineStr">
         <is>
-          <t>快递</t>
+          <t>表达；表示</t>
         </is>
       </c>
       <c r="E1539" s="1" t="inlineStr">
@@ -49547,7 +49683,7 @@
       </c>
       <c r="B1540" s="1" t="inlineStr">
         <is>
-          <t>[ˈtjeɾno] 招标&lt;形&gt;</t>
+          <t>[/ˈtjeɾno/] 温柔的；嫩的；亲切的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1540" s="1" t="inlineStr">
@@ -49557,7 +49693,7 @@
       </c>
       <c r="D1540" s="1" t="inlineStr">
         <is>
-          <t>招标</t>
+          <t>温柔的；嫩的；亲切的</t>
         </is>
       </c>
       <c r="E1540" s="1" t="inlineStr">
@@ -49579,7 +49715,7 @@
       </c>
       <c r="B1541" s="1" t="inlineStr">
         <is>
-          <t>[baˈleɾ] 值得&lt;动&gt;</t>
+          <t>[/baˈleɾ/] 值（多少钱）；有价值&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1541" s="1" t="inlineStr">
@@ -49589,7 +49725,7 @@
       </c>
       <c r="D1541" s="1" t="inlineStr">
         <is>
-          <t>值得</t>
+          <t>值（多少钱）；有价值&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1541" s="1" t="inlineStr">
@@ -49675,7 +49811,7 @@
       </c>
       <c r="B1544" s="1" t="inlineStr">
         <is>
-          <t>[eˈɾiɾ] 受伤&lt;动&gt;</t>
+          <t>[/eˈɾiɾ/] 使受伤；伤害&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1544" s="1" t="inlineStr">
@@ -49685,7 +49821,7 @@
       </c>
       <c r="D1544" s="1" t="inlineStr">
         <is>
-          <t>受伤</t>
+          <t>使受伤；伤害&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1544" s="1" t="inlineStr">
@@ -49835,7 +49971,7 @@
       </c>
       <c r="B1549" s="1" t="inlineStr">
         <is>
-          <t>[pɾetenˈdeɾ] 假装&lt;动&gt;</t>
+          <t>[/pɾetenˈdeɾ/] 企图；试图；声称&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1549" s="1" t="inlineStr">
@@ -49845,7 +49981,7 @@
       </c>
       <c r="D1549" s="1" t="inlineStr">
         <is>
-          <t>假装</t>
+          <t>企图；试图；声称&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1549" s="1" t="inlineStr">
@@ -50091,7 +50227,7 @@
       </c>
       <c r="B1557" s="1" t="inlineStr">
         <is>
-          <t>[esˈkoɾja] 败类&lt;名&gt;</t>
+          <t>[/esˈkoɾja/] 矿渣；熔渣；渣滓&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1557" s="1" t="inlineStr">
@@ -50101,7 +50237,7 @@
       </c>
       <c r="D1557" s="1" t="inlineStr">
         <is>
-          <t>败类</t>
+          <t>矿渣；熔渣；渣滓&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1557" s="1" t="inlineStr">
@@ -50283,7 +50419,7 @@
       </c>
       <c r="B1563" s="1" t="inlineStr">
         <is>
-          <t>[onˈrado] 荣幸的&lt;形&gt;</t>
+          <t>[/onˈrado/] 诚实的；正直的；荣幸的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1563" s="1" t="inlineStr">
@@ -50293,7 +50429,7 @@
       </c>
       <c r="D1563" s="1" t="inlineStr">
         <is>
-          <t>荣幸的</t>
+          <t>诚实的；正直的；荣幸的</t>
         </is>
       </c>
       <c r="E1563" s="1" t="inlineStr">
@@ -50379,7 +50515,7 @@
       </c>
       <c r="B1566" s="1" t="inlineStr">
         <is>
-          <t>[maleˈteɾo] 树干&lt;名&gt;</t>
+          <t>[/maleˈteɾo/] （汽车）后备箱；行李员&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1566" s="1" t="inlineStr">
@@ -50389,7 +50525,7 @@
       </c>
       <c r="D1566" s="1" t="inlineStr">
         <is>
-          <t>树干</t>
+          <t>（汽车）后备箱；行李员</t>
         </is>
       </c>
       <c r="E1566" s="1" t="inlineStr">
@@ -50411,13 +50547,17 @@
       </c>
       <c r="B1567" s="1" t="inlineStr">
         <is>
-          <t>达拉尔&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C1567" s="1" t="inlineStr"/>
+          <t>[[daˈʝaɾ] 割（草）；刈&lt;verb&gt;</t>
+        </is>
+      </c>
+      <c r="C1567" s="1" t="inlineStr">
+        <is>
+          <t>/daʝˈaɾ/</t>
+        </is>
+      </c>
       <c r="D1567" s="1" t="inlineStr">
         <is>
-          <t>达拉尔</t>
+          <t>割（草）；刈</t>
         </is>
       </c>
       <c r="E1567" s="1" t="inlineStr">
@@ -50471,7 +50611,7 @@
       </c>
       <c r="B1569" s="1" t="inlineStr">
         <is>
-          <t>[espeˈθifiko] 具体的&lt;形&gt;</t>
+          <t>[/espeˈθifiko/] 特定的；特有的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1569" s="1" t="inlineStr">
@@ -50481,7 +50621,7 @@
       </c>
       <c r="D1569" s="1" t="inlineStr">
         <is>
-          <t>具体的</t>
+          <t>特定的；特有的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1569" s="1" t="inlineStr">
@@ -50759,7 +50899,7 @@
       </c>
       <c r="B1578" s="1" t="inlineStr">
         <is>
-          <t>[seˈɾeno] 宁静&lt;名&gt;</t>
+          <t>[/seˈɾeno/] 宁静的&lt;形&gt;；守夜人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1578" s="1" t="inlineStr">
@@ -50769,7 +50909,7 @@
       </c>
       <c r="D1578" s="1" t="inlineStr">
         <is>
-          <t>宁静</t>
+          <t>宁静的&lt;形&gt;；守夜人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1578" s="1" t="inlineStr">
@@ -50983,7 +51123,7 @@
       </c>
       <c r="B1585" s="1" t="inlineStr">
         <is>
-          <t>[emˈbidja] 羡慕&lt;名&gt;</t>
+          <t>[/emˈbidja/] 嫉妒；眼红&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1585" s="1" t="inlineStr">
@@ -50993,7 +51133,7 @@
       </c>
       <c r="D1585" s="1" t="inlineStr">
         <is>
-          <t>羡慕</t>
+          <t>嫉妒；眼红&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1585" s="1" t="inlineStr">
@@ -51239,7 +51379,7 @@
       </c>
       <c r="B1593" s="1" t="inlineStr">
         <is>
-          <t>[eˈleno] 海伦&lt;形&gt;</t>
+          <t>[/eˈleno/] 希腊的；希腊人&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1593" s="1" t="inlineStr">
@@ -51249,7 +51389,7 @@
       </c>
       <c r="D1593" s="1" t="inlineStr">
         <is>
-          <t>海伦</t>
+          <t>希腊的；希腊人</t>
         </is>
       </c>
       <c r="E1593" s="1" t="inlineStr">
@@ -51687,7 +51827,7 @@
       </c>
       <c r="B1607" s="1" t="inlineStr">
         <is>
-          <t>[ˈset] 设置&lt;名&gt;</t>
+          <t>[/ˈset/] （网球比赛的）盘；（电影等的）布景、摄制场&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1607" s="1" t="inlineStr">
@@ -51697,7 +51837,7 @@
       </c>
       <c r="D1607" s="1" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>（网球比赛的）盘；（电影等的）布景、摄制场&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1607" s="1" t="inlineStr">
@@ -52007,7 +52147,7 @@
       </c>
       <c r="B1617" s="1" t="inlineStr">
         <is>
-          <t>[monˈtones] 地段&lt;代&gt;</t>
+          <t>[/monˈtones/] 堆；大量&lt;pron&gt;</t>
         </is>
       </c>
       <c r="C1617" s="1" t="inlineStr">
@@ -52017,7 +52157,7 @@
       </c>
       <c r="D1617" s="1" t="inlineStr">
         <is>
-          <t>地段</t>
+          <t>堆；大量</t>
         </is>
       </c>
       <c r="E1617" s="1" t="inlineStr">
@@ -52746,7 +52886,11 @@
           <t>凸轮&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1640" s="1" t="inlineStr"/>
+      <c r="C1640" s="1" t="inlineStr">
+        <is>
+          <t>/kˈam/</t>
+        </is>
+      </c>
       <c r="D1640" s="1" t="inlineStr">
         <is>
           <t>凸轮</t>
@@ -53155,7 +53299,7 @@
       </c>
       <c r="B1653" s="1" t="inlineStr">
         <is>
-          <t>[imbenˈtaɾ] 发明&lt;动&gt;</t>
+          <t>[/imbenˈtaɾ/] 发明&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1653" s="1" t="inlineStr">
@@ -53165,7 +53309,7 @@
       </c>
       <c r="D1653" s="1" t="inlineStr">
         <is>
-          <t>发明</t>
+          <t>发明&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1653" s="1" t="inlineStr">
@@ -53411,7 +53555,7 @@
       </c>
       <c r="B1661" s="1" t="inlineStr">
         <is>
-          <t>[esˈkɾita] 书面的&lt;名&gt;</t>
+          <t>[/esˈkɾita/] escritura [eskɾiˈtuɾa] 书写；笔迹&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1661" s="1" t="inlineStr">
@@ -53421,7 +53565,7 @@
       </c>
       <c r="D1661" s="1" t="inlineStr">
         <is>
-          <t>书面的</t>
+          <t>escritura [eskɾiˈtuɾa] 书写；笔迹&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1661" s="1" t="inlineStr">
@@ -53507,7 +53651,7 @@
       </c>
       <c r="B1664" s="1" t="inlineStr">
         <is>
-          <t>[obliˈɡaɾ] 力&lt;动&gt;</t>
+          <t>[/obliˈɡaɾ/] 强迫；迫使&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1664" s="1" t="inlineStr">
@@ -53517,7 +53661,7 @@
       </c>
       <c r="D1664" s="1" t="inlineStr">
         <is>
-          <t>力</t>
+          <t>强迫；迫使</t>
         </is>
       </c>
       <c r="E1664" s="1" t="inlineStr">
@@ -53923,13 +54067,17 @@
       </c>
       <c r="B1677" s="1" t="inlineStr">
         <is>
-          <t>莫尼科&lt;形&gt;</t>
-        </is>
-      </c>
-      <c r="C1677" s="1" t="inlineStr"/>
+          <t>[[ˈmo.ni.ko] 富有的（非规范词）&lt;adj&gt;</t>
+        </is>
+      </c>
+      <c r="C1677" s="1" t="inlineStr">
+        <is>
+          <t>/mˈoniko/</t>
+        </is>
+      </c>
       <c r="D1677" s="1" t="inlineStr">
         <is>
-          <t>莫尼科</t>
+          <t>富有的（非规范词）</t>
         </is>
       </c>
       <c r="E1677" s="1" t="inlineStr">
@@ -54047,7 +54195,7 @@
       </c>
       <c r="B1681" s="1" t="inlineStr">
         <is>
-          <t>[lut͡ʃaˈdoɾ] 战斗机&lt;名&gt;</t>
+          <t>[/lut͡ʃaˈdoɾ/] 斗士；摔跤手&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1681" s="1" t="inlineStr">
@@ -54057,7 +54205,7 @@
       </c>
       <c r="D1681" s="1" t="inlineStr">
         <is>
-          <t>战斗机</t>
+          <t>斗士；摔跤手</t>
         </is>
       </c>
       <c r="E1681" s="1" t="inlineStr">
@@ -54623,7 +54771,7 @@
       </c>
       <c r="B1699" s="1" t="inlineStr">
         <is>
-          <t>[ˈtaɾdo] 迟到了&lt;形&gt;</t>
+          <t>[/ˈtaɾdo/] 缓慢的；迟缓的&lt;形&gt;（常用形式为 tarde「晚的」）&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1699" s="1" t="inlineStr">
@@ -54633,7 +54781,7 @@
       </c>
       <c r="D1699" s="1" t="inlineStr">
         <is>
-          <t>迟到了</t>
+          <t>缓慢的；迟缓的&lt;形&gt;（常用形式为 tarde「晚的」）</t>
         </is>
       </c>
       <c r="E1699" s="1" t="inlineStr">
@@ -54687,13 +54835,17 @@
       </c>
       <c r="B1701" s="1" t="inlineStr">
         <is>
-          <t>出&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1701" s="1" t="inlineStr"/>
+          <t>[[ˈawt]] 出局&lt;感叹词&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1701" s="1" t="inlineStr">
+        <is>
+          <t>/oˈut/</t>
+        </is>
+      </c>
       <c r="D1701" s="1" t="inlineStr">
         <is>
-          <t>出</t>
+          <t>出局&lt;感叹词&gt;</t>
         </is>
       </c>
       <c r="E1701" s="1" t="inlineStr">
@@ -55390,7 +55542,11 @@
           <t>乍得&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1723" s="1" t="inlineStr"/>
+      <c r="C1723" s="1" t="inlineStr">
+        <is>
+          <t>/tʃˈad/</t>
+        </is>
+      </c>
       <c r="D1723" s="1" t="inlineStr">
         <is>
           <t>乍得</t>
@@ -55415,7 +55571,7 @@
       </c>
       <c r="B1724" s="1" t="inlineStr">
         <is>
-          <t>[ˈxil] 吉尔&lt;名&gt;</t>
+          <t>[/ˈxil/] 傻瓜；蠢人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1724" s="1" t="inlineStr">
@@ -55425,7 +55581,7 @@
       </c>
       <c r="D1724" s="1" t="inlineStr">
         <is>
-          <t>吉尔</t>
+          <t>傻瓜；蠢人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1724" s="1" t="inlineStr">
@@ -55799,7 +55955,7 @@
       </c>
       <c r="B1736" s="1" t="inlineStr">
         <is>
-          <t>[ˈbate] 蝙蝠&lt;名&gt;</t>
+          <t>[/ˈbate/] 球棒；击打&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1736" s="1" t="inlineStr">
@@ -55809,7 +55965,7 @@
       </c>
       <c r="D1736" s="1" t="inlineStr">
         <is>
-          <t>蝙蝠</t>
+          <t>球棒；击打</t>
         </is>
       </c>
       <c r="E1736" s="1" t="inlineStr">
@@ -55831,7 +55987,7 @@
       </c>
       <c r="B1737" s="1" t="inlineStr">
         <is>
-          <t>[luˈnaɾ] 摩尔&lt;名&gt;</t>
+          <t>[/luˈnaɾ/] 痣；月亮的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1737" s="1" t="inlineStr">
@@ -55841,7 +55997,7 @@
       </c>
       <c r="D1737" s="1" t="inlineStr">
         <is>
-          <t>摩尔</t>
+          <t>痣；月亮的</t>
         </is>
       </c>
       <c r="E1737" s="1" t="inlineStr">
@@ -55895,7 +56051,7 @@
       </c>
       <c r="B1739" s="1" t="inlineStr">
         <is>
-          <t>[besˈtiɾ] 连衣裙&lt;动&gt;</t>
+          <t>[/besˈtiɾ/] 穿衣；给…穿衣&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1739" s="1" t="inlineStr">
@@ -55905,7 +56061,7 @@
       </c>
       <c r="D1739" s="1" t="inlineStr">
         <is>
-          <t>连衣裙</t>
+          <t>穿衣；给…穿衣</t>
         </is>
       </c>
       <c r="E1739" s="1" t="inlineStr">
@@ -55991,7 +56147,7 @@
       </c>
       <c r="B1742" s="1" t="inlineStr">
         <is>
-          <t>[maˈɾino] 海洋&lt;名&gt;</t>
+          <t>[/maˈɾino/] 海洋的；海员&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1742" s="1" t="inlineStr">
@@ -56001,7 +56157,7 @@
       </c>
       <c r="D1742" s="1" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>海洋的；海员</t>
         </is>
       </c>
       <c r="E1742" s="1" t="inlineStr">
@@ -56055,7 +56211,7 @@
       </c>
       <c r="B1744" s="1" t="inlineStr">
         <is>
-          <t>[ˌaltaˈmente] 高度&lt;副&gt;</t>
+          <t>[/ˌaltaˈmente/] 高度地；非常&lt;adv&gt;</t>
         </is>
       </c>
       <c r="C1744" s="1" t="inlineStr">
@@ -56065,7 +56221,7 @@
       </c>
       <c r="D1744" s="1" t="inlineStr">
         <is>
-          <t>高度</t>
+          <t>高度地；非常</t>
         </is>
       </c>
       <c r="E1744" s="1" t="inlineStr">
@@ -56663,7 +56819,7 @@
       </c>
       <c r="B1763" s="1" t="inlineStr">
         <is>
-          <t>[kaˈɡaɾ] 狗屎&lt;动&gt;</t>
+          <t>[/kaˈɡaɾ/] 拉屎（粗俗）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1763" s="1" t="inlineStr">
@@ -56673,7 +56829,7 @@
       </c>
       <c r="D1763" s="1" t="inlineStr">
         <is>
-          <t>狗屎</t>
+          <t>拉屎（粗俗）</t>
         </is>
       </c>
       <c r="E1763" s="1" t="inlineStr">
@@ -57687,13 +57843,17 @@
       </c>
       <c r="B1795" s="1" t="inlineStr">
         <is>
-          <t>喇叭&lt;副&gt;</t>
-        </is>
-      </c>
-      <c r="C1795" s="1" t="inlineStr"/>
+          <t>[[ˈkweɾ.nos] 角；犄角&lt;adv&gt;</t>
+        </is>
+      </c>
+      <c r="C1795" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkweɾnos/</t>
+        </is>
+      </c>
       <c r="D1795" s="1" t="inlineStr">
         <is>
-          <t>喇叭</t>
+          <t>角；犄角</t>
         </is>
       </c>
       <c r="E1795" s="1" t="inlineStr">
@@ -59155,7 +59315,7 @@
       </c>
       <c r="B1841" s="1" t="inlineStr">
         <is>
-          <t>[ˈbal] 瓦尔&lt;名&gt;</t>
+          <t>[/ˈbal/] 山谷&lt;名&gt;（诗语）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1841" s="1" t="inlineStr">
@@ -59165,7 +59325,7 @@
       </c>
       <c r="D1841" s="1" t="inlineStr">
         <is>
-          <t>瓦尔</t>
+          <t>山谷&lt;名&gt;（诗语）</t>
         </is>
       </c>
       <c r="E1841" s="1" t="inlineStr">
@@ -59798,7 +59958,11 @@
           <t>你&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C1861" s="1" t="inlineStr"/>
+      <c r="C1861" s="1" t="inlineStr">
+        <is>
+          <t>/usˈtedes/</t>
+        </is>
+      </c>
       <c r="D1861" s="1" t="inlineStr">
         <is>
           <t>你</t>
@@ -59954,7 +60118,11 @@
           <t>米。&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1866" s="1" t="inlineStr"/>
+      <c r="C1866" s="1" t="inlineStr">
+        <is>
+          <t>/ˈmetɾo/</t>
+        </is>
+      </c>
       <c r="D1866" s="1" t="inlineStr">
         <is>
           <t>米。</t>
@@ -60107,7 +60275,7 @@
       </c>
       <c r="B1871" s="1" t="inlineStr">
         <is>
-          <t>[doˈleɾ] 受伤&lt;动&gt;</t>
+          <t>[/doˈleɾ/] 疼痛；使痛苦&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1871" s="1" t="inlineStr">
@@ -60117,7 +60285,7 @@
       </c>
       <c r="D1871" s="1" t="inlineStr">
         <is>
-          <t>受伤</t>
+          <t>疼痛；使痛苦</t>
         </is>
       </c>
       <c r="E1871" s="1" t="inlineStr">
@@ -60939,7 +61107,7 @@
       </c>
       <c r="B1897" s="1" t="inlineStr">
         <is>
-          <t>[ˈkulto] 邪教&lt;名&gt;</t>
+          <t>[/ˈkulto/] 崇拜；有教养的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1897" s="1" t="inlineStr">
@@ -60949,7 +61117,7 @@
       </c>
       <c r="D1897" s="1" t="inlineStr">
         <is>
-          <t>邪教</t>
+          <t>崇拜；有教养的</t>
         </is>
       </c>
       <c r="E1897" s="1" t="inlineStr">
@@ -61262,7 +61430,11 @@
           <t>香槟&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1907" s="1" t="inlineStr"/>
+      <c r="C1907" s="1" t="inlineStr">
+        <is>
+          <t>/tʃampˈaɡne/</t>
+        </is>
+      </c>
       <c r="D1907" s="1" t="inlineStr">
         <is>
           <t>香槟</t>
@@ -61287,7 +61459,7 @@
       </c>
       <c r="B1908" s="1" t="inlineStr">
         <is>
-          <t>[deroˈtaɾ] 失败&lt;动&gt;</t>
+          <t>[/deroˈtaɾ/] 击败；战胜&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1908" s="1" t="inlineStr">
@@ -61297,7 +61469,7 @@
       </c>
       <c r="D1908" s="1" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>击败；战胜</t>
         </is>
       </c>
       <c r="E1908" s="1" t="inlineStr">
@@ -61354,7 +61526,11 @@
           <t>固体&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1910" s="1" t="inlineStr"/>
+      <c r="C1910" s="1" t="inlineStr">
+        <is>
+          <t>/ˈsolido/</t>
+        </is>
+      </c>
       <c r="D1910" s="1" t="inlineStr">
         <is>
           <t>固体</t>
@@ -61667,7 +61843,7 @@
       </c>
       <c r="B1920" s="1" t="inlineStr">
         <is>
-          <t>[ˈθifɾa] 图&lt;名&gt;</t>
+          <t>[/ˈθifɾa/] 数字；数目；位数&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1920" s="1" t="inlineStr">
@@ -61677,7 +61853,7 @@
       </c>
       <c r="D1920" s="1" t="inlineStr">
         <is>
-          <t>图</t>
+          <t>数字；数目；位数</t>
         </is>
       </c>
       <c r="E1920" s="1" t="inlineStr">
@@ -61699,7 +61875,7 @@
       </c>
       <c r="B1921" s="1" t="inlineStr">
         <is>
-          <t>[kaˈt͡ʃoro] 小狗&lt;名&gt;</t>
+          <t>[/kaˈt͡ʃoro/] 幼兽，崽（如小狗、小猫）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1921" s="1" t="inlineStr">
@@ -61709,7 +61885,7 @@
       </c>
       <c r="D1921" s="1" t="inlineStr">
         <is>
-          <t>小狗</t>
+          <t>幼兽，崽（如小狗、小猫）</t>
         </is>
       </c>
       <c r="E1921" s="1" t="inlineStr">
@@ -61763,7 +61939,7 @@
       </c>
       <c r="B1923" s="1" t="inlineStr">
         <is>
-          <t>[ˈfu] 福&lt;叹&gt;</t>
+          <t>[/ˈfu/] 呸；咄（表示厌恶的叹词）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C1923" s="1" t="inlineStr">
@@ -61773,7 +61949,7 @@
       </c>
       <c r="D1923" s="1" t="inlineStr">
         <is>
-          <t>福</t>
+          <t>呸；咄（表示厌恶的叹词）</t>
         </is>
       </c>
       <c r="E1923" s="1" t="inlineStr">
@@ -61987,7 +62163,7 @@
       </c>
       <c r="B1930" s="1" t="inlineStr">
         <is>
-          <t>[renˈdiɾ] 渲染&lt;动&gt;</t>
+          <t>[/renˈdiɾ/] 使屈服；投降；交出；发挥（效能）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1930" s="1" t="inlineStr">
@@ -61997,7 +62173,7 @@
       </c>
       <c r="D1930" s="1" t="inlineStr">
         <is>
-          <t>渲染</t>
+          <t>使屈服；投降；交出；发挥（效能）</t>
         </is>
       </c>
       <c r="E1930" s="1" t="inlineStr">
@@ -62243,7 +62419,7 @@
       </c>
       <c r="B1938" s="1" t="inlineStr">
         <is>
-          <t>[ʝoˈbeɾ] 雨&lt;动&gt;</t>
+          <t>[/ʝoˈbeɾ/] 下雨&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1938" s="1" t="inlineStr">
@@ -62253,7 +62429,7 @@
       </c>
       <c r="D1938" s="1" t="inlineStr">
         <is>
-          <t>雨</t>
+          <t>下雨</t>
         </is>
       </c>
       <c r="E1938" s="1" t="inlineStr">
@@ -62531,7 +62707,7 @@
       </c>
       <c r="B1947" s="1" t="inlineStr">
         <is>
-          <t>[baˈul] 树干&lt;名&gt;</t>
+          <t>[/baˈul/] 箱子；行李箱；后备箱&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1947" s="1" t="inlineStr">
@@ -62541,7 +62717,7 @@
       </c>
       <c r="D1947" s="1" t="inlineStr">
         <is>
-          <t>树干</t>
+          <t>箱子；行李箱；后备箱</t>
         </is>
       </c>
       <c r="E1947" s="1" t="inlineStr">
@@ -63107,7 +63283,7 @@
       </c>
       <c r="B1965" s="1" t="inlineStr">
         <is>
-          <t>[ˈmudo] 愚蠢的&lt;名&gt;</t>
+          <t>[/ˈmudo/] 哑的；无声的；沉默的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1965" s="1" t="inlineStr">
@@ -63117,7 +63293,7 @@
       </c>
       <c r="D1965" s="1" t="inlineStr">
         <is>
-          <t>愚蠢的</t>
+          <t>哑的；无声的；沉默的</t>
         </is>
       </c>
       <c r="E1965" s="1" t="inlineStr">
@@ -63139,7 +63315,7 @@
       </c>
       <c r="B1966" s="1" t="inlineStr">
         <is>
-          <t>[aˈpodo] 昵称&lt;名&gt;</t>
+          <t>[/aˈpodo/] 绰号；外号&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1966" s="1" t="inlineStr">
@@ -63149,7 +63325,7 @@
       </c>
       <c r="D1966" s="1" t="inlineStr">
         <is>
-          <t>昵称</t>
+          <t>绰号；外号&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1966" s="1" t="inlineStr">
@@ -63331,7 +63507,7 @@
       </c>
       <c r="B1972" s="1" t="inlineStr">
         <is>
-          <t>[ˈfuma] 抽烟&lt;名&gt;</t>
+          <t>[/ˈfuma/] fumar 抽烟&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1972" s="1" t="inlineStr">
@@ -63341,7 +63517,7 @@
       </c>
       <c r="D1972" s="1" t="inlineStr">
         <is>
-          <t>抽烟</t>
+          <t>fumar 抽烟&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1972" s="1" t="inlineStr">
@@ -63587,7 +63763,7 @@
       </c>
       <c r="B1980" s="1" t="inlineStr">
         <is>
-          <t>[aˈla] 安拉&lt;叹&gt;</t>
+          <t>[/aˈla/] 安拉；真主&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C1980" s="1" t="inlineStr">
@@ -63597,7 +63773,7 @@
       </c>
       <c r="D1980" s="1" t="inlineStr">
         <is>
-          <t>安拉</t>
+          <t>安拉；真主</t>
         </is>
       </c>
       <c r="E1980" s="1" t="inlineStr">
@@ -63683,7 +63859,7 @@
       </c>
       <c r="B1983" s="1" t="inlineStr">
         <is>
-          <t>[ˈbeɾɡa] 公鸡&lt;名&gt;</t>
+          <t>[/ˈbeɾɡa/] 桅杆；杆；棒&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1983" s="1" t="inlineStr">
@@ -63693,7 +63869,7 @@
       </c>
       <c r="D1983" s="1" t="inlineStr">
         <is>
-          <t>公鸡</t>
+          <t>桅杆；杆；棒</t>
         </is>
       </c>
       <c r="E1983" s="1" t="inlineStr">
@@ -64067,7 +64243,7 @@
       </c>
       <c r="B1995" s="1" t="inlineStr">
         <is>
-          <t>[despeɾˈdiθjo] 废物&lt;名&gt;</t>
+          <t>[/despeɾˈdiθjo/] 浪费&lt;名&gt;；废弃物&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1995" s="1" t="inlineStr">
@@ -64077,7 +64253,7 @@
       </c>
       <c r="D1995" s="1" t="inlineStr">
         <is>
-          <t>废物</t>
+          <t>浪费&lt;名&gt;；废弃物&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1995" s="1" t="inlineStr">
@@ -64355,7 +64531,7 @@
       </c>
       <c r="B2004" s="1" t="inlineStr">
         <is>
-          <t>[nabeˈɡaɾ] 导航&lt;动&gt;</t>
+          <t>[/nabeˈɡaɾ/] 航行；导航&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2004" s="1" t="inlineStr">
@@ -64365,7 +64541,7 @@
       </c>
       <c r="D2004" s="1" t="inlineStr">
         <is>
-          <t>导航</t>
+          <t>航行；导航&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2004" s="1" t="inlineStr">
@@ -64451,7 +64627,7 @@
       </c>
       <c r="B2007" s="1" t="inlineStr">
         <is>
-          <t>[ˈlaθo] 套索&lt;名&gt;</t>
+          <t>[/ˈlaθo/] 蝴蝶结；绳结；套索&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2007" s="1" t="inlineStr">
@@ -64461,7 +64637,7 @@
       </c>
       <c r="D2007" s="1" t="inlineStr">
         <is>
-          <t>套索</t>
+          <t>蝴蝶结；绳结；套索&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2007" s="1" t="inlineStr">
@@ -64515,7 +64691,7 @@
       </c>
       <c r="B2009" s="1" t="inlineStr">
         <is>
-          <t>[alkiˈlaɾ] 租金&lt;动&gt;</t>
+          <t>[/alkiˈlaɾ/] 租用；出租；租赁&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2009" s="1" t="inlineStr">
@@ -64525,7 +64701,7 @@
       </c>
       <c r="D2009" s="1" t="inlineStr">
         <is>
-          <t>租金</t>
+          <t>租用；出租；租赁</t>
         </is>
       </c>
       <c r="E2009" s="1" t="inlineStr">
@@ -65379,7 +65555,7 @@
       </c>
       <c r="B2036" s="1" t="inlineStr">
         <is>
-          <t>[kaɾoˈlino] 卡罗琳&lt;名&gt;</t>
+          <t>[/kaɾoˈlino/] 卡罗来纳的；查理（王朝）的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2036" s="1" t="inlineStr">
@@ -65389,7 +65565,7 @@
       </c>
       <c r="D2036" s="1" t="inlineStr">
         <is>
-          <t>卡罗琳</t>
+          <t>卡罗来纳的；查理（王朝）的</t>
         </is>
       </c>
       <c r="E2036" s="1" t="inlineStr">
@@ -66147,7 +66323,7 @@
       </c>
       <c r="B2060" s="1" t="inlineStr">
         <is>
-          <t>[koloˈɾado] 科罗拉多州&lt;形&gt;</t>
+          <t>[/koloˈɾado/] 红色的；红润的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2060" s="1" t="inlineStr">
@@ -66157,7 +66333,7 @@
       </c>
       <c r="D2060" s="1" t="inlineStr">
         <is>
-          <t>科罗拉多州</t>
+          <t>红色的；红润的</t>
         </is>
       </c>
       <c r="E2060" s="1" t="inlineStr">
@@ -66275,7 +66451,7 @@
       </c>
       <c r="B2064" s="1" t="inlineStr">
         <is>
-          <t>[reˈflexo] 反思&lt;名&gt;</t>
+          <t>[/reˈflexo/] 反射；映像；反映&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2064" s="1" t="inlineStr">
@@ -66285,7 +66461,7 @@
       </c>
       <c r="D2064" s="1" t="inlineStr">
         <is>
-          <t>反思</t>
+          <t>反射；映像；反映</t>
         </is>
       </c>
       <c r="E2064" s="1" t="inlineStr">
@@ -66467,7 +66643,7 @@
       </c>
       <c r="B2070" s="1" t="inlineStr">
         <is>
-          <t>[ˈlote] 很多&lt;名&gt;</t>
+          <t>[/ˈlote/] 一批；一份；地块&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2070" s="1" t="inlineStr">
@@ -66477,7 +66653,7 @@
       </c>
       <c r="D2070" s="1" t="inlineStr">
         <is>
-          <t>很多</t>
+          <t>一批；一份；地块</t>
         </is>
       </c>
       <c r="E2070" s="1" t="inlineStr">
@@ -67747,7 +67923,7 @@
       </c>
       <c r="B2110" s="1" t="inlineStr">
         <is>
-          <t>[puɲeˈtaθo] 冲孔&lt;名&gt;</t>
+          <t>[/puɲeˈtaθo/] 一拳；拳打&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2110" s="1" t="inlineStr">
@@ -67757,7 +67933,7 @@
       </c>
       <c r="D2110" s="1" t="inlineStr">
         <is>
-          <t>冲孔</t>
+          <t>一拳；拳打</t>
         </is>
       </c>
       <c r="E2110" s="1" t="inlineStr">
@@ -67779,7 +67955,7 @@
       </c>
       <c r="B2111" s="1" t="inlineStr">
         <is>
-          <t>[ˈostja] 主机&lt;名&gt;</t>
+          <t>[/ˈostja/] 圣饼；圣体&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2111" s="1" t="inlineStr">
@@ -67789,7 +67965,7 @@
       </c>
       <c r="D2111" s="1" t="inlineStr">
         <is>
-          <t>主机</t>
+          <t>圣饼；圣体</t>
         </is>
       </c>
       <c r="E2111" s="1" t="inlineStr">
@@ -68163,7 +68339,7 @@
       </c>
       <c r="B2123" s="1" t="inlineStr">
         <is>
-          <t>[ˈbando] 侧面&lt;名&gt;</t>
+          <t>[ˈbando] 派系；阵营；公告&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2123" s="1" t="inlineStr">
@@ -68173,7 +68349,7 @@
       </c>
       <c r="D2123" s="1" t="inlineStr">
         <is>
-          <t>侧面</t>
+          <t>派系；阵营；公告</t>
         </is>
       </c>
       <c r="E2123" s="1" t="inlineStr">
@@ -68422,7 +68598,11 @@
           <t>那个&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C2131" s="1" t="inlineStr"/>
+      <c r="C2131" s="1" t="inlineStr">
+        <is>
+          <t>/ˈeso/</t>
+        </is>
+      </c>
       <c r="D2131" s="1" t="inlineStr">
         <is>
           <t>那个</t>
@@ -68607,7 +68787,7 @@
       </c>
       <c r="B2137" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɾuθa] 十字架&lt;名&gt;</t>
+          <t>[ˈkɾuθa] 杂交；杂交种&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2137" s="1" t="inlineStr">
@@ -68617,7 +68797,7 @@
       </c>
       <c r="D2137" s="1" t="inlineStr">
         <is>
-          <t>十字架</t>
+          <t>杂交；杂交种</t>
         </is>
       </c>
       <c r="E2137" s="1" t="inlineStr">
@@ -68863,7 +69043,7 @@
       </c>
       <c r="B2145" s="1" t="inlineStr">
         <is>
-          <t>[ˈram] 公羊&lt;名&gt;</t>
+          <t>[/ˈram/] 内存；随机存取存储器&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2145" s="1" t="inlineStr">
@@ -68873,7 +69053,7 @@
       </c>
       <c r="D2145" s="1" t="inlineStr">
         <is>
-          <t>公羊</t>
+          <t>内存；随机存取存储器</t>
         </is>
       </c>
       <c r="E2145" s="1" t="inlineStr">
@@ -69124,7 +69304,7 @@
       </c>
       <c r="C2153" s="1" t="inlineStr">
         <is>
-          <t>/hoˈɾmi.ɡa/ [hoɾˈmi.ɣ̞a]</t>
+          <t>/hoˈɾmi.ɡa/</t>
         </is>
       </c>
       <c r="D2153" s="1" t="inlineStr">
@@ -69407,7 +69587,7 @@
       </c>
       <c r="B2162" s="1" t="inlineStr">
         <is>
-          <t>[esˈtablo] 稳定&lt;名&gt;</t>
+          <t>[esˈtablo] 马厩；畜栏&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2162" s="1" t="inlineStr">
@@ -69417,7 +69597,7 @@
       </c>
       <c r="D2162" s="1" t="inlineStr">
         <is>
-          <t>稳定</t>
+          <t>马厩；畜栏</t>
         </is>
       </c>
       <c r="E2162" s="1" t="inlineStr">
@@ -69439,7 +69619,7 @@
       </c>
       <c r="B2163" s="1" t="inlineStr">
         <is>
-          <t>[ˈlato] 拉托&lt;形&gt;</t>
+          <t>[ˈlato] 宽的；宽大的；广义的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2163" s="1" t="inlineStr">
@@ -69449,7 +69629,7 @@
       </c>
       <c r="D2163" s="1" t="inlineStr">
         <is>
-          <t>拉托</t>
+          <t>宽的；宽大的；广义的</t>
         </is>
       </c>
       <c r="E2163" s="1" t="inlineStr">
@@ -69567,7 +69747,7 @@
       </c>
       <c r="B2167" s="1" t="inlineStr">
         <is>
-          <t>[kɾisˈtino] 克里斯汀&lt;名&gt;</t>
+          <t>[/kɾisˈtino/] 克里斯蒂娜派支持者（19世纪西班牙支持伊莎贝尔二世及其母克里斯蒂娜摄政者）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2167" s="1" t="inlineStr">
@@ -69577,7 +69757,7 @@
       </c>
       <c r="D2167" s="1" t="inlineStr">
         <is>
-          <t>克里斯汀</t>
+          <t>克里斯蒂娜派支持者（19世纪西班牙支持伊莎贝尔二世及其母克里斯蒂娜摄政者）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2167" s="1" t="inlineStr">
@@ -69599,13 +69779,17 @@
       </c>
       <c r="B2168" s="1" t="inlineStr">
         <is>
-          <t>p。&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2168" s="1" t="inlineStr"/>
+          <t>页&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C2168" s="1" t="inlineStr">
+        <is>
+          <t>/ˈpaxina/</t>
+        </is>
+      </c>
       <c r="D2168" s="1" t="inlineStr">
         <is>
-          <t>p。</t>
+          <t>页</t>
         </is>
       </c>
       <c r="E2168" s="1" t="inlineStr">
@@ -70331,7 +70515,7 @@
       </c>
       <c r="B2191" s="1" t="inlineStr">
         <is>
-          <t>[ˈpipa] 管子&lt;名&gt;</t>
+          <t>[/ˈpipa/] 烟斗；瓜子&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2191" s="1" t="inlineStr">
@@ -70341,7 +70525,7 @@
       </c>
       <c r="D2191" s="1" t="inlineStr">
         <is>
-          <t>管子</t>
+          <t>烟斗；瓜子&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2191" s="1" t="inlineStr">
@@ -70427,13 +70611,17 @@
       </c>
       <c r="B2194" s="1" t="inlineStr">
         <is>
-          <t>是&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2194" s="1" t="inlineStr"/>
+          <t>是（be的过去式）&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C2194" s="1" t="inlineStr">
+        <is>
+          <t>/wˈas/</t>
+        </is>
+      </c>
       <c r="D2194" s="1" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>是（be的过去式）</t>
         </is>
       </c>
       <c r="E2194" s="1" t="inlineStr">
@@ -70839,7 +71027,7 @@
       </c>
       <c r="B2207" s="1" t="inlineStr">
         <is>
-          <t>[reɡaˈlaɾ] 放弃&lt;动&gt;</t>
+          <t>[reɡaˈlaɾ] 赠送；送礼物&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2207" s="1" t="inlineStr">
@@ -70849,7 +71037,7 @@
       </c>
       <c r="D2207" s="1" t="inlineStr">
         <is>
-          <t>放弃</t>
+          <t>赠送；送礼物</t>
         </is>
       </c>
       <c r="E2207" s="1" t="inlineStr">
@@ -70967,7 +71155,7 @@
       </c>
       <c r="B2211" s="1" t="inlineStr">
         <is>
-          <t>[meˈtida] 卡住了&lt;名&gt;</t>
+          <t>[/meˈtida/] 卷入；插手（口语，指介入某事）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2211" s="1" t="inlineStr">
@@ -70977,7 +71165,7 @@
       </c>
       <c r="D2211" s="1" t="inlineStr">
         <is>
-          <t>卡住了</t>
+          <t>卷入；插手（口语，指介入某事）</t>
         </is>
       </c>
       <c r="E2211" s="1" t="inlineStr">
@@ -71383,7 +71571,7 @@
       </c>
       <c r="B2224" s="1" t="inlineStr">
         <is>
-          <t>[konsˈtaɾ] 状态&lt;动&gt;</t>
+          <t>[konsˈtaɾ] 由…组成；由…构成；明确；有记录&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2224" s="1" t="inlineStr">
@@ -71393,7 +71581,7 @@
       </c>
       <c r="D2224" s="1" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>由…组成；由…构成；明确；有记录</t>
         </is>
       </c>
       <c r="E2224" s="1" t="inlineStr">
@@ -71546,7 +71734,11 @@
           <t>迷你&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C2229" s="1" t="inlineStr"/>
+      <c r="C2229" s="1" t="inlineStr">
+        <is>
+          <t>/mˈini/</t>
+        </is>
+      </c>
       <c r="D2229" s="1" t="inlineStr">
         <is>
           <t>迷你</t>
@@ -71891,7 +72083,7 @@
       </c>
       <c r="B2240" s="1" t="inlineStr">
         <is>
-          <t>[respeɡˈtaɾ] 尊重&lt;动&gt;</t>
+          <t>[/respeɡˈtaɾ/] 尊重&lt;动&gt;（正确词形为 respetar）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2240" s="1" t="inlineStr">
@@ -71901,7 +72093,7 @@
       </c>
       <c r="D2240" s="1" t="inlineStr">
         <is>
-          <t>尊重</t>
+          <t>尊重&lt;动&gt;（正确词形为 respetar）</t>
         </is>
       </c>
       <c r="E2240" s="1" t="inlineStr">
@@ -72211,7 +72403,7 @@
       </c>
       <c r="B2250" s="1" t="inlineStr">
         <is>
-          <t>[exekuˈtaɾ] 跑&lt;动&gt;</t>
+          <t>[exekuˈtaɾ] 执行；实施；处决；演奏&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2250" s="1" t="inlineStr">
@@ -72221,7 +72413,7 @@
       </c>
       <c r="D2250" s="1" t="inlineStr">
         <is>
-          <t>跑</t>
+          <t>执行；实施；处决；演奏</t>
         </is>
       </c>
       <c r="E2250" s="1" t="inlineStr">
@@ -72243,7 +72435,7 @@
       </c>
       <c r="B2251" s="1" t="inlineStr">
         <is>
-          <t>[pɾobeˈniɾ] 来吧&lt;动&gt;</t>
+          <t>[pɾobeˈniɾ] 来自；来源于；出自&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2251" s="1" t="inlineStr">
@@ -72253,7 +72445,7 @@
       </c>
       <c r="D2251" s="1" t="inlineStr">
         <is>
-          <t>来吧</t>
+          <t>来自；来源于；出自</t>
         </is>
       </c>
       <c r="E2251" s="1" t="inlineStr">
@@ -72851,7 +73043,7 @@
       </c>
       <c r="B2270" s="1" t="inlineStr">
         <is>
-          <t>[baˈɡon] 马车&lt;名&gt;</t>
+          <t>[baˈɡon] 车厢；货车&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2270" s="1" t="inlineStr">
@@ -72861,7 +73053,7 @@
       </c>
       <c r="D2270" s="1" t="inlineStr">
         <is>
-          <t>马车</t>
+          <t>车厢；货车</t>
         </is>
       </c>
       <c r="E2270" s="1" t="inlineStr">
@@ -73107,7 +73299,7 @@
       </c>
       <c r="B2278" s="1" t="inlineStr">
         <is>
-          <t>[blokeˈaɾ] 块&lt;动&gt;</t>
+          <t>[blokeˈaɾ] 阻挡；封锁；阻塞&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2278" s="1" t="inlineStr">
@@ -73117,7 +73309,7 @@
       </c>
       <c r="D2278" s="1" t="inlineStr">
         <is>
-          <t>块</t>
+          <t>阻挡；封锁；阻塞</t>
         </is>
       </c>
       <c r="E2278" s="1" t="inlineStr">
@@ -73267,7 +73459,7 @@
       </c>
       <c r="B2283" s="1" t="inlineStr">
         <is>
-          <t>[ˈiɾo] 伊罗&lt;名&gt;</t>
+          <t>[ˈiɾo] 铁（hierro 的异体）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2283" s="1" t="inlineStr">
@@ -73277,7 +73469,7 @@
       </c>
       <c r="D2283" s="1" t="inlineStr">
         <is>
-          <t>伊罗</t>
+          <t>铁（hierro 的异体）</t>
         </is>
       </c>
       <c r="E2283" s="1" t="inlineStr">
@@ -73331,7 +73523,7 @@
       </c>
       <c r="B2285" s="1" t="inlineStr">
         <is>
-          <t>[aɡaˈt͡ʃaɾ] 蹲下&lt;动&gt;</t>
+          <t>[/aɡaˈt͡ʃaɾ/] 使弯腰；低头（反身形式 agacharse 蹲下）&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2285" s="1" t="inlineStr">
@@ -73341,7 +73533,7 @@
       </c>
       <c r="D2285" s="1" t="inlineStr">
         <is>
-          <t>蹲下</t>
+          <t>使弯腰；低头（反身形式 agacharse 蹲下）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2285" s="1" t="inlineStr">
@@ -73366,10 +73558,14 @@
           <t>元首&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2286" s="1" t="inlineStr"/>
+      <c r="C2286" s="1" t="inlineStr">
+        <is>
+          <t>/fˈuɾeɾ/</t>
+        </is>
+      </c>
       <c r="D2286" s="1" t="inlineStr">
         <is>
-          <t>元首</t>
+          <t>（非西班牙语词汇，应为 Führer/元首，德语借词，应删除或标注）</t>
         </is>
       </c>
       <c r="E2286" s="1" t="inlineStr">
@@ -73583,7 +73779,7 @@
       </c>
       <c r="B2293" s="1" t="inlineStr">
         <is>
-          <t>[sensaθjoˈnal] 耸人听闻的&lt;形&gt;</t>
+          <t>[/sensaθjoˈnal/] 轰动性的；了不起的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2293" s="1" t="inlineStr">
@@ -73593,7 +73789,7 @@
       </c>
       <c r="D2293" s="1" t="inlineStr">
         <is>
-          <t>耸人听闻的</t>
+          <t>轰动性的；了不起的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2293" s="1" t="inlineStr">
@@ -73871,7 +74067,7 @@
       </c>
       <c r="B2302" s="1" t="inlineStr">
         <is>
-          <t>[esˈtanθja] 留下来&lt;名&gt;</t>
+          <t>[esˈtanθja] 逗留；房间；庄园&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2302" s="1" t="inlineStr">
@@ -73881,7 +74077,7 @@
       </c>
       <c r="D2302" s="1" t="inlineStr">
         <is>
-          <t>留下来</t>
+          <t>逗留；房间；庄园</t>
         </is>
       </c>
       <c r="E2302" s="1" t="inlineStr">
@@ -74031,13 +74227,17 @@
       </c>
       <c r="B2307" s="1" t="inlineStr">
         <is>
-          <t>形式&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2307" s="1" t="inlineStr"/>
+          <t>[[foɾ.mu.laˈɾi.o] 表格；正式的&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2307" s="1" t="inlineStr">
+        <is>
+          <t>/foɾmuˈlaɾjo/</t>
+        </is>
+      </c>
       <c r="D2307" s="1" t="inlineStr">
         <is>
-          <t>形式</t>
+          <t>表格；正式的</t>
         </is>
       </c>
       <c r="E2307" s="1" t="inlineStr">
@@ -74251,7 +74451,7 @@
       </c>
       <c r="B2314" s="1" t="inlineStr">
         <is>
-          <t>[rekoˈreɾ] 游览&lt;动&gt;</t>
+          <t>[/rekoˈreɾ/] 走遍；巡视；穿越&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2314" s="1" t="inlineStr">
@@ -74261,7 +74461,7 @@
       </c>
       <c r="D2314" s="1" t="inlineStr">
         <is>
-          <t>游览</t>
+          <t>走遍；巡视；穿越&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2314" s="1" t="inlineStr">
@@ -74603,7 +74803,7 @@
       </c>
       <c r="B2325" s="1" t="inlineStr">
         <is>
-          <t>[ˈnasa] 美国航空航天局&lt;名&gt;</t>
+          <t>[/ˈnasa/] 鱼笼；捕鱼篓&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2325" s="1" t="inlineStr">
@@ -74613,7 +74813,7 @@
       </c>
       <c r="D2325" s="1" t="inlineStr">
         <is>
-          <t>美国航空航天局</t>
+          <t>鱼笼；捕鱼篓</t>
         </is>
       </c>
       <c r="E2325" s="1" t="inlineStr">
@@ -74731,7 +74931,7 @@
       </c>
       <c r="B2329" s="1" t="inlineStr">
         <is>
-          <t>[moˈlaɾ] 臼齿&lt;名&gt;</t>
+          <t>[/moˈlaɾ/] 磨牙&lt;名&gt;；（俚语）使喜欢&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2329" s="1" t="inlineStr">
@@ -74741,7 +74941,7 @@
       </c>
       <c r="D2329" s="1" t="inlineStr">
         <is>
-          <t>臼齿</t>
+          <t>磨牙&lt;名&gt;；（俚语）使喜欢&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2329" s="1" t="inlineStr">
@@ -74795,7 +74995,7 @@
       </c>
       <c r="B2331" s="1" t="inlineStr">
         <is>
-          <t>[maˈsibo] 巨大的&lt;形&gt;</t>
+          <t>[/maˈsibo/] 大规模的&lt;形&gt;；大量的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2331" s="1" t="inlineStr">
@@ -74805,7 +75005,7 @@
       </c>
       <c r="D2331" s="1" t="inlineStr">
         <is>
-          <t>巨大的</t>
+          <t>大规模的&lt;形&gt;；大量的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2331" s="1" t="inlineStr">
@@ -74923,7 +75123,7 @@
       </c>
       <c r="B2335" s="1" t="inlineStr">
         <is>
-          <t>[ˈfino] 很好&lt;形&gt;</t>
+          <t>[/ˈfino/] 细的；精致的；优良的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2335" s="1" t="inlineStr">
@@ -74933,7 +75133,7 @@
       </c>
       <c r="D2335" s="1" t="inlineStr">
         <is>
-          <t>很好</t>
+          <t>细的；精致的；优良的</t>
         </is>
       </c>
       <c r="E2335" s="1" t="inlineStr">
@@ -75157,7 +75357,7 @@
       </c>
       <c r="D2342" s="1" t="inlineStr">
         <is>
-          <t>数据</t>
+          <t>（西语应为 fecha）日期；data 非西班牙语词</t>
         </is>
       </c>
       <c r="E2342" s="1" t="inlineStr">
@@ -75598,7 +75798,11 @@
           <t>队长&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2356" s="1" t="inlineStr"/>
+      <c r="C2356" s="1" t="inlineStr">
+        <is>
+          <t>/kapˈitan/</t>
+        </is>
+      </c>
       <c r="D2356" s="1" t="inlineStr">
         <is>
           <t>队长</t>
@@ -76071,7 +76275,7 @@
       </c>
       <c r="B2371" s="1" t="inlineStr">
         <is>
-          <t>[ˈpika] 异食癖&lt;名&gt;</t>
+          <t>[/ˈpika/] 镐；鹤嘴锄&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2371" s="1" t="inlineStr">
@@ -76081,7 +76285,7 @@
       </c>
       <c r="D2371" s="1" t="inlineStr">
         <is>
-          <t>异食癖</t>
+          <t>镐；鹤嘴锄&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2371" s="1" t="inlineStr">
@@ -76199,7 +76403,7 @@
       </c>
       <c r="B2375" s="1" t="inlineStr">
         <is>
-          <t>[tɾaˈmaɾ] 情节&lt;动&gt;</t>
+          <t>[/tɾaˈmaɾ/] 密谋；策划&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2375" s="1" t="inlineStr">
@@ -76209,7 +76413,7 @@
       </c>
       <c r="D2375" s="1" t="inlineStr">
         <is>
-          <t>情节</t>
+          <t>密谋；策划</t>
         </is>
       </c>
       <c r="E2375" s="1" t="inlineStr">
@@ -76231,7 +76435,7 @@
       </c>
       <c r="B2376" s="1" t="inlineStr">
         <is>
-          <t>[ˈluk] 看看&lt;名&gt;</t>
+          <t>[/ˈluk/] 造型；外观&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2376" s="1" t="inlineStr">
@@ -76241,7 +76445,7 @@
       </c>
       <c r="D2376" s="1" t="inlineStr">
         <is>
-          <t>看看</t>
+          <t>造型；外观</t>
         </is>
       </c>
       <c r="E2376" s="1" t="inlineStr">
@@ -76615,7 +76819,7 @@
       </c>
       <c r="B2388" s="1" t="inlineStr">
         <is>
-          <t>[ˈaba] 艾娃&lt;名&gt;</t>
+          <t>[/ˈaba/] 艾娃（人名）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2388" s="1" t="inlineStr">
@@ -76625,7 +76829,7 @@
       </c>
       <c r="D2388" s="1" t="inlineStr">
         <is>
-          <t>艾娃</t>
+          <t>艾娃（人名）</t>
         </is>
       </c>
       <c r="E2388" s="1" t="inlineStr">
@@ -76778,7 +76982,11 @@
           <t>呵呵&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C2393" s="1" t="inlineStr"/>
+      <c r="C2393" s="1" t="inlineStr">
+        <is>
+          <t>/xˈe/</t>
+        </is>
+      </c>
       <c r="D2393" s="1" t="inlineStr">
         <is>
           <t>呵呵</t>
@@ -77027,7 +77235,7 @@
       </c>
       <c r="B2401" s="1" t="inlineStr">
         <is>
-          <t>[ˈkweɾno] 号角&lt;名&gt;</t>
+          <t>[/ˈkweɾno/] 角；兽角&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2401" s="1" t="inlineStr">
@@ -77037,7 +77245,7 @@
       </c>
       <c r="D2401" s="1" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>角；兽角&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2401" s="1" t="inlineStr">
@@ -77382,7 +77590,11 @@
           <t>公元&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C2412" s="1" t="inlineStr"/>
+      <c r="C2412" s="1" t="inlineStr">
+        <is>
+          <t>/ˈde ˈse/</t>
+        </is>
+      </c>
       <c r="D2412" s="1" t="inlineStr">
         <is>
           <t>公元</t>
@@ -77503,7 +77715,7 @@
       </c>
       <c r="B2416" s="1" t="inlineStr">
         <is>
-          <t>[ˈbeɾo] 维罗&lt;名&gt;</t>
+          <t>[/ˈbeɾo/] 确实；真正地&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2416" s="1" t="inlineStr">
@@ -77513,7 +77725,7 @@
       </c>
       <c r="D2416" s="1" t="inlineStr">
         <is>
-          <t>维罗</t>
+          <t>确实；真正地</t>
         </is>
       </c>
       <c r="E2416" s="1" t="inlineStr">
@@ -77599,7 +77811,7 @@
       </c>
       <c r="B2419" s="1" t="inlineStr">
         <is>
-          <t>[suspenˈdido] 暂停&lt;形&gt;</t>
+          <t>[/suspenˈdido/] 被暂停的；被中止的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2419" s="1" t="inlineStr">
@@ -77609,7 +77821,7 @@
       </c>
       <c r="D2419" s="1" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>被暂停的；被中止的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2419" s="1" t="inlineStr">
@@ -78050,7 +78262,11 @@
           <t>费尔南多&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2433" s="1" t="inlineStr"/>
+      <c r="C2433" s="1" t="inlineStr">
+        <is>
+          <t>/feɾnando/</t>
+        </is>
+      </c>
       <c r="D2433" s="1" t="inlineStr">
         <is>
           <t>费尔南多</t>
@@ -78171,7 +78387,7 @@
       </c>
       <c r="B2437" s="1" t="inlineStr">
         <is>
-          <t>[eskoˈθes] 苏格兰威士忌&lt;名&gt;</t>
+          <t>[/eskoˈθes/] 苏格兰的；苏格兰人&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2437" s="1" t="inlineStr">
@@ -78181,7 +78397,7 @@
       </c>
       <c r="D2437" s="1" t="inlineStr">
         <is>
-          <t>苏格兰威士忌</t>
+          <t>苏格兰的；苏格兰人</t>
         </is>
       </c>
       <c r="E2437" s="1" t="inlineStr">
@@ -78715,7 +78931,7 @@
       </c>
       <c r="B2454" s="1" t="inlineStr">
         <is>
-          <t>[musiˈkaɾ] 音乐&lt;动&gt;</t>
+          <t>[/musiˈkaɾ/] 作曲；演奏音乐&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2454" s="1" t="inlineStr">
@@ -78725,7 +78941,7 @@
       </c>
       <c r="D2454" s="1" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>作曲；演奏音乐</t>
         </is>
       </c>
       <c r="E2454" s="1" t="inlineStr">
@@ -78782,7 +78998,11 @@
           <t>赫拉克勒斯&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2456" s="1" t="inlineStr"/>
+      <c r="C2456" s="1" t="inlineStr">
+        <is>
+          <t>/ˈeɾkules/</t>
+        </is>
+      </c>
       <c r="D2456" s="1" t="inlineStr">
         <is>
           <t>赫拉克勒斯</t>
@@ -78903,7 +79123,7 @@
       </c>
       <c r="B2460" s="1" t="inlineStr">
         <is>
-          <t>[naˈtal] 本地人&lt;形&gt;</t>
+          <t>[/naˈtal/] 出生的；出生地的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2460" s="1" t="inlineStr">
@@ -78913,7 +79133,7 @@
       </c>
       <c r="D2460" s="1" t="inlineStr">
         <is>
-          <t>本地人</t>
+          <t>出生的；出生地的</t>
         </is>
       </c>
       <c r="E2460" s="1" t="inlineStr">
@@ -79287,13 +79507,17 @@
       </c>
       <c r="B2472" s="1" t="inlineStr">
         <is>
-          <t>引擎盖&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2472" s="1" t="inlineStr"/>
+          <t>[[ˈxuð] 兜帽；风帽&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2472" s="1" t="inlineStr">
+        <is>
+          <t>/oˈod/</t>
+        </is>
+      </c>
       <c r="D2472" s="1" t="inlineStr">
         <is>
-          <t>引擎盖</t>
+          <t>兜帽；风帽</t>
         </is>
       </c>
       <c r="E2472" s="1" t="inlineStr">
@@ -79315,7 +79539,7 @@
       </c>
       <c r="B2473" s="1" t="inlineStr">
         <is>
-          <t>[unibeɾˈsal] 通用的&lt;形&gt;</t>
+          <t>[/unibeɾˈsal/] 通用的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2473" s="1" t="inlineStr">
@@ -79325,7 +79549,7 @@
       </c>
       <c r="D2473" s="1" t="inlineStr">
         <is>
-          <t>通用的</t>
+          <t>通用的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2473" s="1" t="inlineStr">
@@ -79859,7 +80083,7 @@
       </c>
       <c r="B2490" s="1" t="inlineStr">
         <is>
-          <t>[ˈblusa] 衬衫&lt;名&gt;</t>
+          <t>[/ˈblusa/] 女衬衫&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2490" s="1" t="inlineStr">
@@ -79869,7 +80093,7 @@
       </c>
       <c r="D2490" s="1" t="inlineStr">
         <is>
-          <t>衬衫</t>
+          <t>女衬衫&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2490" s="1" t="inlineStr">
